--- a/00_スケジュール/KSM_AWS_SCH_001_AWS改修スケジュール.xlsx
+++ b/00_スケジュール/KSM_AWS_SCH_001_AWS改修スケジュール.xlsx
@@ -1,30 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kitkat44g-my.sharepoint.com/personal/kiyohara_kadutoshi_com1/Documents/●kasumi_pos-server/00_スケジュール/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_B76BB4C195306B643B07804C3F3B3A5F1695D162" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{391F2D8E-0E42-43C1-A426-78221BF90284}"/>
+  <xr:revisionPtr revIDLastSave="136" documentId="11_B76BB4C195306B643B07804C3F3B3A5F1695D162" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6A2AC56-6958-4D7F-AE11-29091E9CCC81}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AWS改修スケジュール" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="242">
   <si>
     <t>AWS改修・リポジトリ統合スケジュール（1名体制）</t>
   </si>
   <si>
+    <t>Luvina_Có phải sửa không</t>
+  </si>
+  <si>
+    <t>Luvina_Đánh giá</t>
+  </si>
+  <si>
     <t>2026/03</t>
   </si>
   <si>
@@ -211,24 +233,49 @@
     <t>BFGで履歴からも削除</t>
   </si>
   <si>
+    <t>Không sửa</t>
+  </si>
+  <si>
+    <t>#1 Giá trị mặc định đang trỏ tới máy test local. Ví dụ username: ${DB_USERNAME:posuser} thì username sẽ lấy từ biến môi trường DB_USERNAME trên máy, còn username = posuser chỉ là giá trị trên máy test local =&gt; Đánh giá ở đây là không phải sửa</t>
+  </si>
+  <si>
     <t>#2 HARD_TOKEN削除・JWTシークレット新規生成</t>
   </si>
   <si>
     <t>既存トークン全無効化・再ログイン必要</t>
   </si>
   <si>
+    <t>Sửa</t>
+  </si>
+  <si>
+    <t>#2 Đánh giá có thể thể chuyển vào biến môi trường trong máy</t>
+  </si>
+  <si>
     <t>▶ Phase 2: 高優先度（1〜2週間以内）</t>
   </si>
   <si>
     <t>#3 webpackプロキシ 2バックエンド対応</t>
   </si>
   <si>
+    <t>#3 Cấu hình proxy này chỉ dành cho môi trường development trên localhost, từ là khi web localhost start với port 9060 và thực hiện call api nó sẽ điều chuyển sang localhost:8080, vì server local nó chạy ở port 808
+=&gt; Đánh giá đây không phải là vấn đề</t>
+  </si>
+  <si>
     <t>#4 HikariCP minimumIdle 設定バグ修正</t>
   </si>
   <si>
+    <t>Hiện tại source code đang để mặc định là 
+minimum-idle: 5
+=&gt; Đánh giá đây không phải là vấn đề</t>
+  </si>
+  <si>
     <t>#5 CORS設定 本番ドメイン限定</t>
   </si>
   <si>
+    <t>trong code không có allowedOrigins("*"), và đang lấy biến môi trường CORS_ALLOWED_ORIGINS = https://stg.ignicapos.com, tức chỉ có web này mới truy truy cập được api server
+=&gt; Đánh giá đây không phải là vấn đề</t>
+  </si>
+  <si>
     <t>▶ Phase 3: 中優先度（3〜4週間以内）</t>
   </si>
   <si>
@@ -238,21 +285,37 @@
     <t>2026-03-30</t>
   </si>
   <si>
+    <t>#6 Đánh giá không cần thiết vì version server hiện tại đang ổn định, nếu nâng version phải đánh giá các thư viện và có thể rủi ro lỗi khi chạy</t>
+  </si>
+  <si>
     <t>#7 単体テスト追加</t>
   </si>
   <si>
     <t>2026-04-06</t>
   </si>
   <si>
+    <t>#7 Chưa cần thiết vì code đã được tester thực hiện test, hoặc có thể là ưu tiên thấp nếu vẫn muốn sửa</t>
+  </si>
+  <si>
     <t>#8 デバッグコード削除</t>
   </si>
   <si>
+    <t>#8 qua kiểm tra soure code backend frontend thì không có chỗ nào để user/password tạm test</t>
+  </si>
+  <si>
     <t>#9 Flyway 有効化</t>
   </si>
   <si>
+    <t>#9 Do Mr.Kiyohara sửa trực tiếp các bảng trong database không thông qua code nên phải spring.flyway.enabled=false, tức là code sẽ không trực tiếp sửa tên bảng trong BB</t>
+  </si>
+  <si>
     <t>#10 Hibernate dialect 修正</t>
   </si>
   <si>
+    <t>#10 Đánh giá có thể xóa dòng
+spring.jpa.properties.hibernate.dialect=org.hibernate.dialect.MySQL8Dialect</t>
+  </si>
+  <si>
     <t>▶ Phase 4: 低優先度（2〜3ヶ月以内）</t>
   </si>
   <si>
@@ -262,6 +325,9 @@
     <t>2026-05-11</t>
   </si>
   <si>
+    <t>#11,12 Liên quan đến tạo mono repo và CI/CD và đang thực làm trong tài liệu</t>
+  </si>
+  <si>
     <t>#12 pos-server Dockerfile 作成</t>
   </si>
   <si>
@@ -271,15 +337,29 @@
     <t>2026-05-25</t>
   </si>
   <si>
+    <t>#13 Không có hardecode \ (kiểu đường dẫn file Windows) trong code java, chỉ có trong file application.yml có để các đường dẫn mặc định trên windows, tuy nhiên các trường đó là lấy từ biến môi trường trên máy
+ ví dụ cấu hình 
+dir: ${LOG_UPLOAD_DIR:C:/Logs/Gift} là sẽ lấy từ biến môi trường LOG_UPLOAD_DIR còn không có biến môi trường là lấy mặc định</t>
+  </si>
+  <si>
     <t>#14 外部URL 環境変数化</t>
   </si>
   <si>
+    <t>#14 Trong source code không có ký tự nào về fujifilm</t>
+  </si>
+  <si>
     <t>#15 staging差分マージ</t>
   </si>
   <si>
     <t>2026-06-08</t>
   </si>
   <si>
+    <t>Chưa hiểu ý</t>
+  </si>
+  <si>
+    <t>#15 repo pos-server-frontend-ishida-staging về web gift card và đổi giá khẩn cấp chưa có phát triển production, không biết ở đây là so sánh với repo nào</t>
+  </si>
+  <si>
     <t>AWS インフラ改修</t>
   </si>
   <si>
@@ -292,6 +372,14 @@
     <t>現状確認・変更コマンド準備</t>
   </si>
   <si>
+    <t>Đánh giá sau</t>
+  </si>
+  <si>
+    <t>Cài đặt backup hiện tại chỉ lưu trữ 1 ngày, khi xảy ra sự cố chỉ có thể 
+khôi phục snapshot của ngày hôm trước. 
+ Phạm vi làm cả 2 môi trường STG/PRD =&gt; ở đây cần đánh giá chi tiết hơn</t>
+  </si>
+  <si>
     <t>RDS BackupRetentionPeriod 変更（7日以上）</t>
   </si>
   <si>
@@ -313,6 +401,9 @@
     <t>月次自動保持ルール作成</t>
   </si>
   <si>
+    <t>Tạo bản snapshot tự động =&gt; do có phát sinh chi phí $20~$30 / tháng nên tài liệu này phải đưa cho khách hàng duyệt rồi mới triển khai</t>
+  </si>
+  <si>
     <t>AWS Backup プラン作成・リソース割り当て</t>
   </si>
   <si>
@@ -334,6 +425,9 @@
     <t>現在の環境変数・動作確認</t>
   </si>
   <si>
+    <t>Lambda này (create-file-end-for-night) chỉ thực hiện SELECT, là xử lý chỉ đọc. Chuyển sang Reader endpoint để giảm tải cho Writer</t>
+  </si>
+  <si>
     <t>Lambda環境変数変更（DB_KASUMI → RO）</t>
   </si>
   <si>
@@ -355,6 +449,9 @@
     <t>フェイルオーバー動作に影響なし</t>
   </si>
   <si>
+    <t>NangLD đánh giá</t>
+  </si>
+  <si>
     <t>変更後の確認</t>
   </si>
   <si>
@@ -370,6 +467,13 @@
     <t>改修指示書 20260308-003 使用</t>
   </si>
   <si>
+    <t>Nên làm</t>
+  </si>
+  <si>
+    <t>Ở đây đề xuất với khách hàng để bật tắt tự động server sftp để giảm chi phí.
+ Phương án là bật server sftp luồng OC, SG từ 20h tới 7h sáng hôm sau bằng cách là  EventBridge Scheduler + Lambda</t>
+  </si>
+  <si>
     <t>承認取得</t>
   </si>
   <si>
@@ -409,6 +513,12 @@
     <t>06_コスト調査レポート使用</t>
   </si>
   <si>
+    <t>Nên thử nghiệm trên staging trước</t>
+  </si>
+  <si>
+    <t>Đây là ý tường giảm cấu hình RDS để giảm chi phí AWS -&gt; cần phải trình bày với KH hàng</t>
+  </si>
+  <si>
     <t>カスミ様・BIPROGY様</t>
   </si>
   <si>
@@ -460,6 +570,13 @@
     <t>影響範囲調査（全Lambda・ECS参照確認）</t>
   </si>
   <si>
+    <t>Ưu tiên thấp</t>
+  </si>
+  <si>
+    <t>Hiện tại, đặt tên Secrets Manager không thống nhất giữa PRD/STG. Thống nhất quy tắc đặt tên và di chuyển tham chiếu biến môi trường Lambda theo từng giai đoạn.
+Điều tra có đặt tên có đúng theo quy tắc</t>
+  </si>
+  <si>
     <t>変更計画・移行手順書作成</t>
   </si>
   <si>
@@ -523,6 +640,9 @@
     <t>[A] ★障害復旧★ DELETE→SF手動再実行→正常完了確認（2d）</t>
   </si>
   <si>
+    <t>Cần phải có cơ chế backup, không nên lưu tất cả history vào DB và không có cơ chế xóa, đây là nguyên nhân để đầy bộ nhớ và làm insert/update/query db sẽ bị chậm</t>
+  </si>
+  <si>
     <t>SFTP秘密鍵更新</t>
   </si>
   <si>
@@ -533,6 +653,9 @@
   </si>
   <si>
     <t>[B] ishida JAR→専用ユーザーでsystemd化（1.5d）</t>
+  </si>
+  <si>
+    <t>Không chạy server bằng super su</t>
   </si>
   <si>
     <t>aws_022</t>
@@ -656,10 +779,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="m/d/yyyy"/>
-  </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -733,6 +853,13 @@
     <font>
       <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="BIZ UDPゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -889,7 +1016,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -938,7 +1065,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -971,7 +1098,7 @@
     <xf numFmtId="0" fontId="7" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -984,35 +1111,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1035,10 +1154,31 @@
     <xf numFmtId="49" fontId="2" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1050,9 +1190,11 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1315,7 +1457,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF335"/>
-  <sheetFormatPr defaultColWidth="5" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="5" defaultRowHeight="11.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="42" style="2" customWidth="1"/>
@@ -1323,37 +1465,44 @@
     <col min="5" max="5" width="10" style="2" customWidth="1"/>
     <col min="6" max="6" width="25" style="3" customWidth="1"/>
     <col min="7" max="7" width="5" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="5" style="2"/>
+    <col min="8" max="23" width="5" style="2"/>
+    <col min="24" max="24" width="13.28515625" style="40" customWidth="1"/>
+    <col min="25" max="25" width="63.7109375" style="39" customWidth="1"/>
+    <col min="26" max="16384" width="5" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="36" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y1" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="Z1" s="5"/>
       <c r="AA1" s="5"/>
       <c r="AB1" s="5"/>
@@ -1369,131 +1518,135 @@
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="59" t="s">
-        <v>2</v>
-      </c>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="41" t="s">
+      <c r="G2" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="51" t="s">
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="42"/>
-      <c r="W2" s="42"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="57" t="s">
+        <v>5</v>
+      </c>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="64"/>
+      <c r="S2" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="T2" s="64"/>
+      <c r="U2" s="64"/>
+      <c r="V2" s="64"/>
+      <c r="W2" s="64"/>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="38"/>
     </row>
     <row r="3" spans="1:32" s="5" customFormat="1" ht="25.5" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>27</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="38"/>
     </row>
     <row r="4" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A4" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
+      <c r="A4" s="61" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="63"/>
+      <c r="Q4" s="63"/>
+      <c r="R4" s="63"/>
+      <c r="S4" s="63"/>
+      <c r="T4" s="63"/>
+      <c r="U4" s="63"/>
+      <c r="V4" s="63"/>
+      <c r="W4" s="63"/>
+      <c r="X4" s="19"/>
+      <c r="Y4" s="38"/>
       <c r="Z4" s="5"/>
       <c r="AA4" s="5"/>
       <c r="AB4" s="5"/>
@@ -1503,33 +1656,33 @@
       <c r="AF4" s="5"/>
     </row>
     <row r="5" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A5" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
+      <c r="A5" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="63"/>
+      <c r="S5" s="63"/>
+      <c r="T5" s="63"/>
+      <c r="U5" s="63"/>
+      <c r="V5" s="63"/>
+      <c r="W5" s="63"/>
+      <c r="X5" s="19"/>
+      <c r="Y5" s="38"/>
       <c r="Z5" s="5"/>
       <c r="AA5" s="5"/>
       <c r="AB5" s="5"/>
@@ -1540,23 +1693,23 @@
     </row>
     <row r="6" spans="1:32" ht="24" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
@@ -1574,8 +1727,8 @@
       <c r="U6" s="19"/>
       <c r="V6" s="19"/>
       <c r="W6" s="19"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="38"/>
       <c r="Z6" s="5"/>
       <c r="AA6" s="5"/>
       <c r="AB6" s="5"/>
@@ -1586,23 +1739,23 @@
     </row>
     <row r="7" spans="1:32" ht="14.1" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F7" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="18" t="s">
         <v>37</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>35</v>
       </c>
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
@@ -1620,8 +1773,8 @@
       <c r="U7" s="19"/>
       <c r="V7" s="19"/>
       <c r="W7" s="19"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="38"/>
       <c r="Z7" s="5"/>
       <c r="AA7" s="5"/>
       <c r="AB7" s="5"/>
@@ -1632,26 +1785,26 @@
     </row>
     <row r="8" spans="1:32" ht="24" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" s="20"/>
       <c r="E8" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
@@ -1668,8 +1821,8 @@
       <c r="U8" s="19"/>
       <c r="V8" s="19"/>
       <c r="W8" s="19"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
+      <c r="X8" s="19"/>
+      <c r="Y8" s="38"/>
       <c r="Z8" s="5"/>
       <c r="AA8" s="5"/>
       <c r="AB8" s="5"/>
@@ -1680,26 +1833,26 @@
     </row>
     <row r="9" spans="1:32" ht="14.1" customHeight="1">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>41</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>39</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="19"/>
@@ -1716,8 +1869,8 @@
       <c r="U9" s="19"/>
       <c r="V9" s="19"/>
       <c r="W9" s="19"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="38"/>
       <c r="Z9" s="5"/>
       <c r="AA9" s="5"/>
       <c r="AB9" s="5"/>
@@ -1728,24 +1881,24 @@
     </row>
     <row r="10" spans="1:32" ht="24" customHeight="1">
       <c r="A10" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G10" s="19"/>
       <c r="H10" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
@@ -1762,8 +1915,8 @@
       <c r="U10" s="19"/>
       <c r="V10" s="19"/>
       <c r="W10" s="19"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="38"/>
       <c r="Z10" s="5"/>
       <c r="AA10" s="5"/>
       <c r="AB10" s="5"/>
@@ -1773,33 +1926,33 @@
       <c r="AF10" s="5"/>
     </row>
     <row r="11" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A11" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="38"/>
-      <c r="S11" s="38"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
+      <c r="A11" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="63"/>
+      <c r="O11" s="63"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
+      <c r="R11" s="63"/>
+      <c r="S11" s="63"/>
+      <c r="T11" s="63"/>
+      <c r="U11" s="63"/>
+      <c r="V11" s="63"/>
+      <c r="W11" s="63"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="38"/>
       <c r="Z11" s="5"/>
       <c r="AA11" s="5"/>
       <c r="AB11" s="5"/>
@@ -1810,22 +1963,22 @@
     </row>
     <row r="12" spans="1:32" ht="18" customHeight="1">
       <c r="A12" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F12" s="17"/>
       <c r="G12" s="19"/>
       <c r="H12" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I12" s="19"/>
       <c r="J12" s="19"/>
@@ -1842,8 +1995,8 @@
       <c r="U12" s="19"/>
       <c r="V12" s="19"/>
       <c r="W12" s="19"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="38"/>
       <c r="Z12" s="5"/>
       <c r="AA12" s="5"/>
       <c r="AB12" s="5"/>
@@ -1854,24 +2007,24 @@
     </row>
     <row r="13" spans="1:32" ht="18" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G13" s="19"/>
       <c r="H13" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I13" s="19"/>
       <c r="J13" s="19"/>
@@ -1888,8 +2041,8 @@
       <c r="U13" s="19"/>
       <c r="V13" s="19"/>
       <c r="W13" s="19"/>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="5"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="38"/>
       <c r="Z13" s="5"/>
       <c r="AA13" s="5"/>
       <c r="AB13" s="5"/>
@@ -1900,25 +2053,25 @@
     </row>
     <row r="14" spans="1:32" ht="18" customHeight="1">
       <c r="A14" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
       <c r="I14" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J14" s="19"/>
       <c r="K14" s="19"/>
@@ -1934,8 +2087,8 @@
       <c r="U14" s="19"/>
       <c r="V14" s="19"/>
       <c r="W14" s="19"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5"/>
+      <c r="X14" s="19"/>
+      <c r="Y14" s="38"/>
       <c r="Z14" s="5"/>
       <c r="AA14" s="5"/>
       <c r="AB14" s="5"/>
@@ -1946,25 +2099,25 @@
     </row>
     <row r="15" spans="1:32" ht="18" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
       <c r="I15" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J15" s="19"/>
       <c r="K15" s="19"/>
@@ -1980,8 +2133,8 @@
       <c r="U15" s="19"/>
       <c r="V15" s="19"/>
       <c r="W15" s="19"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="38"/>
       <c r="Z15" s="5"/>
       <c r="AA15" s="5"/>
       <c r="AB15" s="5"/>
@@ -1991,33 +2144,33 @@
       <c r="AF15" s="5"/>
     </row>
     <row r="16" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A16" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="38"/>
-      <c r="R16" s="38"/>
-      <c r="S16" s="38"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="38"/>
-      <c r="W16" s="38"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5"/>
+      <c r="A16" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="63"/>
+      <c r="L16" s="63"/>
+      <c r="M16" s="63"/>
+      <c r="N16" s="63"/>
+      <c r="O16" s="63"/>
+      <c r="P16" s="63"/>
+      <c r="Q16" s="63"/>
+      <c r="R16" s="63"/>
+      <c r="S16" s="63"/>
+      <c r="T16" s="63"/>
+      <c r="U16" s="63"/>
+      <c r="V16" s="63"/>
+      <c r="W16" s="63"/>
+      <c r="X16" s="19"/>
+      <c r="Y16" s="38"/>
       <c r="Z16" s="5"/>
       <c r="AA16" s="5"/>
       <c r="AB16" s="5"/>
@@ -2027,33 +2180,33 @@
       <c r="AF16" s="5"/>
     </row>
     <row r="17" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A17" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="38"/>
-      <c r="R17" s="38"/>
-      <c r="S17" s="38"/>
-      <c r="T17" s="38"/>
-      <c r="U17" s="38"/>
-      <c r="V17" s="38"/>
-      <c r="W17" s="38"/>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="5"/>
+      <c r="A17" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
+      <c r="L17" s="63"/>
+      <c r="M17" s="63"/>
+      <c r="N17" s="63"/>
+      <c r="O17" s="63"/>
+      <c r="P17" s="63"/>
+      <c r="Q17" s="63"/>
+      <c r="R17" s="63"/>
+      <c r="S17" s="63"/>
+      <c r="T17" s="63"/>
+      <c r="U17" s="63"/>
+      <c r="V17" s="63"/>
+      <c r="W17" s="63"/>
+      <c r="X17" s="19"/>
+      <c r="Y17" s="38"/>
       <c r="Z17" s="5"/>
       <c r="AA17" s="5"/>
       <c r="AB17" s="5"/>
@@ -2062,25 +2215,25 @@
       <c r="AE17" s="5"/>
       <c r="AF17" s="5"/>
     </row>
-    <row r="18" spans="1:32" ht="18" customHeight="1">
+    <row r="18" spans="1:32" ht="58.5" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -2098,8 +2251,12 @@
       <c r="U18" s="19"/>
       <c r="V18" s="19"/>
       <c r="W18" s="19"/>
-      <c r="X18" s="5"/>
-      <c r="Y18" s="5"/>
+      <c r="X18" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y18" s="38" t="s">
+        <v>66</v>
+      </c>
       <c r="Z18" s="5"/>
       <c r="AA18" s="5"/>
       <c r="AB18" s="5"/>
@@ -2110,23 +2267,23 @@
     </row>
     <row r="19" spans="1:32" ht="24" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B19" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>63</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>61</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H19" s="19"/>
       <c r="I19" s="19"/>
@@ -2144,8 +2301,12 @@
       <c r="U19" s="19"/>
       <c r="V19" s="19"/>
       <c r="W19" s="19"/>
-      <c r="X19" s="5"/>
-      <c r="Y19" s="5"/>
+      <c r="X19" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y19" s="38" t="s">
+        <v>70</v>
+      </c>
       <c r="Z19" s="5"/>
       <c r="AA19" s="5"/>
       <c r="AB19" s="5"/>
@@ -2155,33 +2316,33 @@
       <c r="AF19" s="5"/>
     </row>
     <row r="20" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A20" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38"/>
-      <c r="R20" s="38"/>
-      <c r="S20" s="38"/>
-      <c r="T20" s="38"/>
-      <c r="U20" s="38"/>
-      <c r="V20" s="38"/>
-      <c r="W20" s="38"/>
-      <c r="X20" s="5"/>
-      <c r="Y20" s="5"/>
+      <c r="A20" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="63"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="63"/>
+      <c r="L20" s="63"/>
+      <c r="M20" s="63"/>
+      <c r="N20" s="63"/>
+      <c r="O20" s="63"/>
+      <c r="P20" s="63"/>
+      <c r="Q20" s="63"/>
+      <c r="R20" s="63"/>
+      <c r="S20" s="63"/>
+      <c r="T20" s="63"/>
+      <c r="U20" s="63"/>
+      <c r="V20" s="63"/>
+      <c r="W20" s="63"/>
+      <c r="X20" s="19"/>
+      <c r="Y20" s="38"/>
       <c r="Z20" s="5"/>
       <c r="AA20" s="5"/>
       <c r="AB20" s="5"/>
@@ -2190,27 +2351,27 @@
       <c r="AE20" s="5"/>
       <c r="AF20" s="5"/>
     </row>
-    <row r="21" spans="1:32" ht="18" customHeight="1">
+    <row r="21" spans="1:32" ht="72" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F21" s="17"/>
       <c r="G21" s="19"/>
       <c r="H21" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J21" s="19"/>
       <c r="K21" s="19"/>
@@ -2226,8 +2387,12 @@
       <c r="U21" s="19"/>
       <c r="V21" s="19"/>
       <c r="W21" s="19"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5"/>
+      <c r="X21" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y21" s="38" t="s">
+        <v>73</v>
+      </c>
       <c r="Z21" s="5"/>
       <c r="AA21" s="5"/>
       <c r="AB21" s="5"/>
@@ -2236,27 +2401,27 @@
       <c r="AE21" s="5"/>
       <c r="AF21" s="5"/>
     </row>
-    <row r="22" spans="1:32" ht="18" customHeight="1">
+    <row r="22" spans="1:32" ht="56.25" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D22" s="20"/>
       <c r="E22" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F22" s="17"/>
       <c r="G22" s="19"/>
       <c r="H22" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I22" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J22" s="19"/>
       <c r="K22" s="19"/>
@@ -2272,8 +2437,12 @@
       <c r="U22" s="19"/>
       <c r="V22" s="19"/>
       <c r="W22" s="19"/>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5"/>
+      <c r="X22" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y22" s="38" t="s">
+        <v>75</v>
+      </c>
       <c r="Z22" s="5"/>
       <c r="AA22" s="5"/>
       <c r="AB22" s="5"/>
@@ -2282,27 +2451,27 @@
       <c r="AE22" s="5"/>
       <c r="AF22" s="5"/>
     </row>
-    <row r="23" spans="1:32" ht="18" customHeight="1">
+    <row r="23" spans="1:32" ht="64.5" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D23" s="20"/>
       <c r="E23" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F23" s="17"/>
       <c r="G23" s="19"/>
       <c r="H23" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I23" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J23" s="19"/>
       <c r="K23" s="19"/>
@@ -2318,8 +2487,12 @@
       <c r="U23" s="19"/>
       <c r="V23" s="19"/>
       <c r="W23" s="19"/>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5"/>
+      <c r="X23" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y23" s="38" t="s">
+        <v>77</v>
+      </c>
       <c r="Z23" s="5"/>
       <c r="AA23" s="5"/>
       <c r="AB23" s="5"/>
@@ -2329,33 +2502,33 @@
       <c r="AF23" s="5"/>
     </row>
     <row r="24" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A24" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="38"/>
-      <c r="Q24" s="38"/>
-      <c r="R24" s="38"/>
-      <c r="S24" s="38"/>
-      <c r="T24" s="38"/>
-      <c r="U24" s="38"/>
-      <c r="V24" s="38"/>
-      <c r="W24" s="38"/>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5"/>
+      <c r="A24" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="63"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="63"/>
+      <c r="K24" s="63"/>
+      <c r="L24" s="63"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="63"/>
+      <c r="P24" s="63"/>
+      <c r="Q24" s="63"/>
+      <c r="R24" s="63"/>
+      <c r="S24" s="63"/>
+      <c r="T24" s="63"/>
+      <c r="U24" s="63"/>
+      <c r="V24" s="63"/>
+      <c r="W24" s="63"/>
+      <c r="X24" s="19"/>
+      <c r="Y24" s="38"/>
       <c r="Z24" s="5"/>
       <c r="AA24" s="5"/>
       <c r="AB24" s="5"/>
@@ -2364,28 +2537,28 @@
       <c r="AE24" s="5"/>
       <c r="AF24" s="5"/>
     </row>
-    <row r="25" spans="1:32" ht="18" customHeight="1">
+    <row r="25" spans="1:32" ht="45" customHeight="1">
       <c r="A25" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F25" s="17"/>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
       <c r="I25" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J25" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K25" s="19"/>
       <c r="L25" s="19"/>
@@ -2400,8 +2573,12 @@
       <c r="U25" s="19"/>
       <c r="V25" s="19"/>
       <c r="W25" s="19"/>
-      <c r="X25" s="5"/>
-      <c r="Y25" s="5"/>
+      <c r="X25" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y25" s="38" t="s">
+        <v>81</v>
+      </c>
       <c r="Z25" s="5"/>
       <c r="AA25" s="5"/>
       <c r="AB25" s="5"/>
@@ -2410,29 +2587,29 @@
       <c r="AE25" s="5"/>
       <c r="AF25" s="5"/>
     </row>
-    <row r="26" spans="1:32" ht="18" customHeight="1">
+    <row r="26" spans="1:32" ht="28.5" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D26" s="20"/>
       <c r="E26" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F26" s="17"/>
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K26" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L26" s="19"/>
       <c r="M26" s="19"/>
@@ -2446,8 +2623,12 @@
       <c r="U26" s="19"/>
       <c r="V26" s="19"/>
       <c r="W26" s="19"/>
-      <c r="X26" s="5"/>
-      <c r="Y26" s="5"/>
+      <c r="X26" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y26" s="38" t="s">
+        <v>84</v>
+      </c>
       <c r="Z26" s="5"/>
       <c r="AA26" s="5"/>
       <c r="AB26" s="5"/>
@@ -2456,29 +2637,29 @@
       <c r="AE26" s="5"/>
       <c r="AF26" s="5"/>
     </row>
-    <row r="27" spans="1:32" ht="18" customHeight="1">
+    <row r="27" spans="1:32" ht="33.75" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D27" s="20"/>
       <c r="E27" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F27" s="17"/>
       <c r="G27" s="19"/>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
       <c r="J27" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K27" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L27" s="19"/>
       <c r="M27" s="19"/>
@@ -2492,8 +2673,12 @@
       <c r="U27" s="19"/>
       <c r="V27" s="19"/>
       <c r="W27" s="19"/>
-      <c r="X27" s="5"/>
-      <c r="Y27" s="5"/>
+      <c r="X27" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y27" s="38" t="s">
+        <v>86</v>
+      </c>
       <c r="Z27" s="5"/>
       <c r="AA27" s="5"/>
       <c r="AB27" s="5"/>
@@ -2502,29 +2687,29 @@
       <c r="AE27" s="5"/>
       <c r="AF27" s="5"/>
     </row>
-    <row r="28" spans="1:32" ht="18" customHeight="1">
+    <row r="28" spans="1:32" ht="52.5" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D28" s="20"/>
       <c r="E28" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F28" s="17"/>
       <c r="G28" s="19"/>
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
       <c r="J28" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K28" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L28" s="19"/>
       <c r="M28" s="19"/>
@@ -2538,8 +2723,12 @@
       <c r="U28" s="19"/>
       <c r="V28" s="19"/>
       <c r="W28" s="19"/>
-      <c r="X28" s="5"/>
-      <c r="Y28" s="5"/>
+      <c r="X28" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y28" s="38" t="s">
+        <v>88</v>
+      </c>
       <c r="Z28" s="5"/>
       <c r="AA28" s="5"/>
       <c r="AB28" s="5"/>
@@ -2548,29 +2737,29 @@
       <c r="AE28" s="5"/>
       <c r="AF28" s="5"/>
     </row>
-    <row r="29" spans="1:32" ht="18" customHeight="1">
+    <row r="29" spans="1:32" ht="39" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F29" s="17"/>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
       <c r="J29" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K29" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L29" s="19"/>
       <c r="M29" s="19"/>
@@ -2584,8 +2773,12 @@
       <c r="U29" s="19"/>
       <c r="V29" s="19"/>
       <c r="W29" s="19"/>
-      <c r="X29" s="5"/>
-      <c r="Y29" s="5"/>
+      <c r="X29" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y29" s="38" t="s">
+        <v>90</v>
+      </c>
       <c r="Z29" s="5"/>
       <c r="AA29" s="5"/>
       <c r="AB29" s="5"/>
@@ -2595,33 +2788,33 @@
       <c r="AF29" s="5"/>
     </row>
     <row r="30" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A30" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" s="38"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="38"/>
-      <c r="K30" s="38"/>
-      <c r="L30" s="38"/>
-      <c r="M30" s="38"/>
-      <c r="N30" s="38"/>
-      <c r="O30" s="38"/>
-      <c r="P30" s="38"/>
-      <c r="Q30" s="38"/>
-      <c r="R30" s="38"/>
-      <c r="S30" s="38"/>
-      <c r="T30" s="38"/>
-      <c r="U30" s="38"/>
-      <c r="V30" s="38"/>
-      <c r="W30" s="38"/>
-      <c r="X30" s="5"/>
-      <c r="Y30" s="5"/>
+      <c r="A30" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="63"/>
+      <c r="C30" s="63"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
+      <c r="K30" s="63"/>
+      <c r="L30" s="63"/>
+      <c r="M30" s="63"/>
+      <c r="N30" s="63"/>
+      <c r="O30" s="63"/>
+      <c r="P30" s="63"/>
+      <c r="Q30" s="63"/>
+      <c r="R30" s="63"/>
+      <c r="S30" s="63"/>
+      <c r="T30" s="63"/>
+      <c r="U30" s="63"/>
+      <c r="V30" s="63"/>
+      <c r="W30" s="63"/>
+      <c r="X30" s="19"/>
+      <c r="Y30" s="38"/>
       <c r="Z30" s="5"/>
       <c r="AA30" s="5"/>
       <c r="AB30" s="5"/>
@@ -2630,19 +2823,19 @@
       <c r="AE30" s="5"/>
       <c r="AF30" s="5"/>
     </row>
-    <row r="31" spans="1:32" ht="18" customHeight="1">
+    <row r="31" spans="1:32" ht="39" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F31" s="17"/>
       <c r="G31" s="19"/>
@@ -2654,10 +2847,10 @@
       <c r="M31" s="19"/>
       <c r="N31" s="19"/>
       <c r="O31" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P31" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
@@ -2666,8 +2859,12 @@
       <c r="U31" s="19"/>
       <c r="V31" s="19"/>
       <c r="W31" s="19"/>
-      <c r="X31" s="5"/>
-      <c r="Y31" s="5"/>
+      <c r="X31" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y31" s="38" t="s">
+        <v>94</v>
+      </c>
       <c r="Z31" s="5"/>
       <c r="AA31" s="5"/>
       <c r="AB31" s="5"/>
@@ -2676,19 +2873,19 @@
       <c r="AE31" s="5"/>
       <c r="AF31" s="5"/>
     </row>
-    <row r="32" spans="1:32" ht="18" customHeight="1">
+    <row r="32" spans="1:32" ht="37.5" customHeight="1">
       <c r="A32" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D32" s="20"/>
       <c r="E32" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F32" s="17"/>
       <c r="G32" s="19"/>
@@ -2700,10 +2897,10 @@
       <c r="M32" s="19"/>
       <c r="N32" s="19"/>
       <c r="O32" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P32" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q32" s="19"/>
       <c r="R32" s="19"/>
@@ -2712,8 +2909,12 @@
       <c r="U32" s="19"/>
       <c r="V32" s="19"/>
       <c r="W32" s="19"/>
-      <c r="X32" s="5"/>
-      <c r="Y32" s="5"/>
+      <c r="X32" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y32" s="38" t="s">
+        <v>94</v>
+      </c>
       <c r="Z32" s="5"/>
       <c r="AA32" s="5"/>
       <c r="AB32" s="5"/>
@@ -2722,19 +2923,19 @@
       <c r="AE32" s="5"/>
       <c r="AF32" s="5"/>
     </row>
-    <row r="33" spans="1:32" ht="18" customHeight="1">
+    <row r="33" spans="1:32" ht="78" customHeight="1">
       <c r="A33" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D33" s="15"/>
       <c r="E33" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F33" s="17"/>
       <c r="G33" s="19"/>
@@ -2748,18 +2949,22 @@
       <c r="O33" s="19"/>
       <c r="P33" s="19"/>
       <c r="Q33" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R33" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="S33" s="19"/>
       <c r="T33" s="19"/>
       <c r="U33" s="19"/>
       <c r="V33" s="19"/>
       <c r="W33" s="19"/>
-      <c r="X33" s="5"/>
-      <c r="Y33" s="5"/>
+      <c r="X33" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y33" s="38" t="s">
+        <v>98</v>
+      </c>
       <c r="Z33" s="5"/>
       <c r="AA33" s="5"/>
       <c r="AB33" s="5"/>
@@ -2770,17 +2975,17 @@
     </row>
     <row r="34" spans="1:32" ht="18" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D34" s="20"/>
       <c r="E34" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F34" s="17"/>
       <c r="G34" s="19"/>
@@ -2794,18 +2999,22 @@
       <c r="O34" s="19"/>
       <c r="P34" s="19"/>
       <c r="Q34" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R34" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="S34" s="19"/>
       <c r="T34" s="19"/>
       <c r="U34" s="19"/>
       <c r="V34" s="19"/>
       <c r="W34" s="19"/>
-      <c r="X34" s="5"/>
-      <c r="Y34" s="5"/>
+      <c r="X34" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y34" s="38" t="s">
+        <v>100</v>
+      </c>
       <c r="Z34" s="5"/>
       <c r="AA34" s="5"/>
       <c r="AB34" s="5"/>
@@ -2814,19 +3023,19 @@
       <c r="AE34" s="5"/>
       <c r="AF34" s="5"/>
     </row>
-    <row r="35" spans="1:32" ht="18" customHeight="1">
+    <row r="35" spans="1:32" ht="53.25" customHeight="1">
       <c r="A35" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="D35" s="20"/>
       <c r="E35" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F35" s="17"/>
       <c r="G35" s="19"/>
@@ -2842,16 +3051,20 @@
       <c r="Q35" s="19"/>
       <c r="R35" s="19"/>
       <c r="S35" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="T35" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="U35" s="19"/>
       <c r="V35" s="19"/>
       <c r="W35" s="19"/>
-      <c r="X35" s="5"/>
-      <c r="Y35" s="5"/>
+      <c r="X35" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y35" s="38" t="s">
+        <v>104</v>
+      </c>
       <c r="Z35" s="5"/>
       <c r="AA35" s="5"/>
       <c r="AB35" s="5"/>
@@ -2861,33 +3074,33 @@
       <c r="AF35" s="5"/>
     </row>
     <row r="36" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A36" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="38"/>
-      <c r="M36" s="38"/>
-      <c r="N36" s="38"/>
-      <c r="O36" s="38"/>
-      <c r="P36" s="38"/>
-      <c r="Q36" s="38"/>
-      <c r="R36" s="38"/>
-      <c r="S36" s="38"/>
-      <c r="T36" s="38"/>
-      <c r="U36" s="38"/>
-      <c r="V36" s="38"/>
-      <c r="W36" s="38"/>
-      <c r="X36" s="5"/>
-      <c r="Y36" s="5"/>
+      <c r="A36" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="63"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="63"/>
+      <c r="K36" s="63"/>
+      <c r="L36" s="63"/>
+      <c r="M36" s="63"/>
+      <c r="N36" s="63"/>
+      <c r="O36" s="63"/>
+      <c r="P36" s="63"/>
+      <c r="Q36" s="63"/>
+      <c r="R36" s="63"/>
+      <c r="S36" s="63"/>
+      <c r="T36" s="63"/>
+      <c r="U36" s="63"/>
+      <c r="V36" s="63"/>
+      <c r="W36" s="63"/>
+      <c r="X36" s="19"/>
+      <c r="Y36" s="38"/>
       <c r="Z36" s="5"/>
       <c r="AA36" s="5"/>
       <c r="AB36" s="5"/>
@@ -2897,33 +3110,33 @@
       <c r="AF36" s="5"/>
     </row>
     <row r="37" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A37" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="38"/>
-      <c r="L37" s="38"/>
-      <c r="M37" s="38"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="38"/>
-      <c r="P37" s="38"/>
-      <c r="Q37" s="38"/>
-      <c r="R37" s="38"/>
-      <c r="S37" s="38"/>
-      <c r="T37" s="38"/>
-      <c r="U37" s="38"/>
-      <c r="V37" s="38"/>
-      <c r="W37" s="38"/>
-      <c r="X37" s="5"/>
-      <c r="Y37" s="5"/>
+      <c r="A37" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" s="63"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="63"/>
+      <c r="J37" s="63"/>
+      <c r="K37" s="63"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="63"/>
+      <c r="O37" s="63"/>
+      <c r="P37" s="63"/>
+      <c r="Q37" s="63"/>
+      <c r="R37" s="63"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="63"/>
+      <c r="U37" s="63"/>
+      <c r="V37" s="63"/>
+      <c r="W37" s="63"/>
+      <c r="X37" s="19"/>
+      <c r="Y37" s="38"/>
       <c r="Z37" s="5"/>
       <c r="AA37" s="5"/>
       <c r="AB37" s="5"/>
@@ -2932,23 +3145,23 @@
       <c r="AE37" s="5"/>
       <c r="AF37" s="5"/>
     </row>
-    <row r="38" spans="1:32" ht="18" customHeight="1">
+    <row r="38" spans="1:32" ht="56.25" customHeight="1">
       <c r="A38" s="13" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D38" s="15"/>
       <c r="E38" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F38" s="17"/>
       <c r="G38" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H38" s="19"/>
       <c r="I38" s="19"/>
@@ -2966,8 +3179,12 @@
       <c r="U38" s="19"/>
       <c r="V38" s="19"/>
       <c r="W38" s="19"/>
-      <c r="X38" s="5"/>
-      <c r="Y38" s="5"/>
+      <c r="X38" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y38" s="38" t="s">
+        <v>110</v>
+      </c>
       <c r="Z38" s="5"/>
       <c r="AA38" s="5"/>
       <c r="AB38" s="5"/>
@@ -2978,23 +3195,23 @@
     </row>
     <row r="39" spans="1:32" ht="18" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D39" s="15"/>
       <c r="E39" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
@@ -3012,8 +3229,8 @@
       <c r="U39" s="19"/>
       <c r="V39" s="19"/>
       <c r="W39" s="19"/>
-      <c r="X39" s="5"/>
-      <c r="Y39" s="5"/>
+      <c r="X39" s="19"/>
+      <c r="Y39" s="38"/>
       <c r="Z39" s="5"/>
       <c r="AA39" s="5"/>
       <c r="AB39" s="5"/>
@@ -3024,22 +3241,22 @@
     </row>
     <row r="40" spans="1:32" ht="18" customHeight="1">
       <c r="A40" s="13" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D40" s="15"/>
       <c r="E40" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F40" s="17"/>
       <c r="G40" s="19"/>
       <c r="H40" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I40" s="19"/>
       <c r="J40" s="19"/>
@@ -3056,8 +3273,8 @@
       <c r="U40" s="19"/>
       <c r="V40" s="19"/>
       <c r="W40" s="19"/>
-      <c r="X40" s="5"/>
-      <c r="Y40" s="5"/>
+      <c r="X40" s="19"/>
+      <c r="Y40" s="38"/>
       <c r="Z40" s="5"/>
       <c r="AA40" s="5"/>
       <c r="AB40" s="5"/>
@@ -3067,33 +3284,33 @@
       <c r="AF40" s="5"/>
     </row>
     <row r="41" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A41" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="B41" s="38"/>
-      <c r="C41" s="38"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="38"/>
-      <c r="J41" s="38"/>
-      <c r="K41" s="38"/>
-      <c r="L41" s="38"/>
-      <c r="M41" s="38"/>
-      <c r="N41" s="38"/>
-      <c r="O41" s="38"/>
-      <c r="P41" s="38"/>
-      <c r="Q41" s="38"/>
-      <c r="R41" s="38"/>
-      <c r="S41" s="38"/>
-      <c r="T41" s="38"/>
-      <c r="U41" s="38"/>
-      <c r="V41" s="38"/>
-      <c r="W41" s="38"/>
-      <c r="X41" s="5"/>
-      <c r="Y41" s="5"/>
+      <c r="A41" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" s="63"/>
+      <c r="C41" s="63"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
+      <c r="I41" s="63"/>
+      <c r="J41" s="63"/>
+      <c r="K41" s="63"/>
+      <c r="L41" s="63"/>
+      <c r="M41" s="63"/>
+      <c r="N41" s="63"/>
+      <c r="O41" s="63"/>
+      <c r="P41" s="63"/>
+      <c r="Q41" s="63"/>
+      <c r="R41" s="63"/>
+      <c r="S41" s="63"/>
+      <c r="T41" s="63"/>
+      <c r="U41" s="63"/>
+      <c r="V41" s="63"/>
+      <c r="W41" s="63"/>
+      <c r="X41" s="19"/>
+      <c r="Y41" s="38"/>
       <c r="Z41" s="5"/>
       <c r="AA41" s="5"/>
       <c r="AB41" s="5"/>
@@ -3102,26 +3319,26 @@
       <c r="AE41" s="5"/>
       <c r="AF41" s="5"/>
     </row>
-    <row r="42" spans="1:32" ht="18" customHeight="1">
+    <row r="42" spans="1:32" ht="52.5" customHeight="1">
       <c r="A42" s="13" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D42" s="20"/>
       <c r="E42" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="G42" s="19"/>
       <c r="H42" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I42" s="19"/>
       <c r="J42" s="19"/>
@@ -3138,8 +3355,12 @@
       <c r="U42" s="19"/>
       <c r="V42" s="19"/>
       <c r="W42" s="19"/>
-      <c r="X42" s="5"/>
-      <c r="Y42" s="5"/>
+      <c r="X42" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y42" s="38" t="s">
+        <v>118</v>
+      </c>
       <c r="Z42" s="5"/>
       <c r="AA42" s="5"/>
       <c r="AB42" s="5"/>
@@ -3150,23 +3371,23 @@
     </row>
     <row r="43" spans="1:32" ht="18" customHeight="1">
       <c r="A43" s="13" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="D43" s="20"/>
       <c r="E43" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F43" s="17"/>
       <c r="G43" s="19"/>
       <c r="H43" s="19"/>
       <c r="I43" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J43" s="19"/>
       <c r="K43" s="19"/>
@@ -3182,8 +3403,8 @@
       <c r="U43" s="19"/>
       <c r="V43" s="19"/>
       <c r="W43" s="19"/>
-      <c r="X43" s="5"/>
-      <c r="Y43" s="5"/>
+      <c r="X43" s="19"/>
+      <c r="Y43" s="38"/>
       <c r="Z43" s="5"/>
       <c r="AA43" s="5"/>
       <c r="AB43" s="5"/>
@@ -3194,24 +3415,24 @@
     </row>
     <row r="44" spans="1:32" ht="18" customHeight="1">
       <c r="A44" s="13" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D44" s="20"/>
       <c r="E44" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F44" s="17"/>
       <c r="G44" s="19"/>
       <c r="H44" s="19"/>
       <c r="I44" s="19"/>
       <c r="J44" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K44" s="19"/>
       <c r="L44" s="19"/>
@@ -3226,8 +3447,8 @@
       <c r="U44" s="19"/>
       <c r="V44" s="19"/>
       <c r="W44" s="19"/>
-      <c r="X44" s="5"/>
-      <c r="Y44" s="5"/>
+      <c r="X44" s="19"/>
+      <c r="Y44" s="38"/>
       <c r="Z44" s="5"/>
       <c r="AA44" s="5"/>
       <c r="AB44" s="5"/>
@@ -3237,33 +3458,33 @@
       <c r="AF44" s="5"/>
     </row>
     <row r="45" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A45" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="B45" s="38"/>
-      <c r="C45" s="38"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="39"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="38"/>
-      <c r="I45" s="38"/>
-      <c r="J45" s="38"/>
-      <c r="K45" s="38"/>
-      <c r="L45" s="38"/>
-      <c r="M45" s="38"/>
-      <c r="N45" s="38"/>
-      <c r="O45" s="38"/>
-      <c r="P45" s="38"/>
-      <c r="Q45" s="38"/>
-      <c r="R45" s="38"/>
-      <c r="S45" s="38"/>
-      <c r="T45" s="38"/>
-      <c r="U45" s="38"/>
-      <c r="V45" s="38"/>
-      <c r="W45" s="38"/>
-      <c r="X45" s="5"/>
-      <c r="Y45" s="5"/>
+      <c r="A45" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="63"/>
+      <c r="C45" s="63"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="63"/>
+      <c r="I45" s="63"/>
+      <c r="J45" s="63"/>
+      <c r="K45" s="63"/>
+      <c r="L45" s="63"/>
+      <c r="M45" s="63"/>
+      <c r="N45" s="63"/>
+      <c r="O45" s="63"/>
+      <c r="P45" s="63"/>
+      <c r="Q45" s="63"/>
+      <c r="R45" s="63"/>
+      <c r="S45" s="63"/>
+      <c r="T45" s="63"/>
+      <c r="U45" s="63"/>
+      <c r="V45" s="63"/>
+      <c r="W45" s="63"/>
+      <c r="X45" s="19"/>
+      <c r="Y45" s="38"/>
       <c r="Z45" s="5"/>
       <c r="AA45" s="5"/>
       <c r="AB45" s="5"/>
@@ -3273,33 +3494,33 @@
       <c r="AF45" s="5"/>
     </row>
     <row r="46" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A46" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="B46" s="38"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="39"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
-      <c r="J46" s="38"/>
-      <c r="K46" s="38"/>
-      <c r="L46" s="38"/>
-      <c r="M46" s="38"/>
-      <c r="N46" s="38"/>
-      <c r="O46" s="38"/>
-      <c r="P46" s="38"/>
-      <c r="Q46" s="38"/>
-      <c r="R46" s="38"/>
-      <c r="S46" s="38"/>
-      <c r="T46" s="38"/>
-      <c r="U46" s="38"/>
-      <c r="V46" s="38"/>
-      <c r="W46" s="38"/>
-      <c r="X46" s="5"/>
-      <c r="Y46" s="5"/>
+      <c r="A46" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="63"/>
+      <c r="C46" s="63"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="63"/>
+      <c r="J46" s="63"/>
+      <c r="K46" s="63"/>
+      <c r="L46" s="63"/>
+      <c r="M46" s="63"/>
+      <c r="N46" s="63"/>
+      <c r="O46" s="63"/>
+      <c r="P46" s="63"/>
+      <c r="Q46" s="63"/>
+      <c r="R46" s="63"/>
+      <c r="S46" s="63"/>
+      <c r="T46" s="63"/>
+      <c r="U46" s="63"/>
+      <c r="V46" s="63"/>
+      <c r="W46" s="63"/>
+      <c r="X46" s="19"/>
+      <c r="Y46" s="38"/>
       <c r="Z46" s="5"/>
       <c r="AA46" s="5"/>
       <c r="AB46" s="5"/>
@@ -3308,23 +3529,23 @@
       <c r="AE46" s="5"/>
       <c r="AF46" s="5"/>
     </row>
-    <row r="47" spans="1:32" ht="18" customHeight="1">
+    <row r="47" spans="1:32" ht="33.75" customHeight="1">
       <c r="A47" s="13" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D47" s="20"/>
       <c r="E47" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F47" s="17"/>
       <c r="G47" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H47" s="19"/>
       <c r="I47" s="19"/>
@@ -3342,8 +3563,12 @@
       <c r="U47" s="19"/>
       <c r="V47" s="19"/>
       <c r="W47" s="19"/>
-      <c r="X47" s="5"/>
-      <c r="Y47" s="5"/>
+      <c r="X47" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y47" s="38" t="s">
+        <v>126</v>
+      </c>
       <c r="Z47" s="5"/>
       <c r="AA47" s="5"/>
       <c r="AB47" s="5"/>
@@ -3354,23 +3579,23 @@
     </row>
     <row r="48" spans="1:32" ht="18" customHeight="1">
       <c r="A48" s="13" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D48" s="20"/>
       <c r="E48" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H48" s="19"/>
       <c r="I48" s="19"/>
@@ -3388,8 +3613,10 @@
       <c r="U48" s="19"/>
       <c r="V48" s="19"/>
       <c r="W48" s="19"/>
-      <c r="X48" s="5"/>
-      <c r="Y48" s="5"/>
+      <c r="X48" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y48" s="38"/>
       <c r="Z48" s="5"/>
       <c r="AA48" s="5"/>
       <c r="AB48" s="5"/>
@@ -3400,22 +3627,22 @@
     </row>
     <row r="49" spans="1:32" ht="18" customHeight="1">
       <c r="A49" s="13" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D49" s="20"/>
       <c r="E49" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F49" s="17"/>
       <c r="G49" s="19"/>
       <c r="H49" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I49" s="19"/>
       <c r="J49" s="19"/>
@@ -3432,8 +3659,10 @@
       <c r="U49" s="19"/>
       <c r="V49" s="19"/>
       <c r="W49" s="19"/>
-      <c r="X49" s="5"/>
-      <c r="Y49" s="5"/>
+      <c r="X49" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y49" s="38"/>
       <c r="Z49" s="5"/>
       <c r="AA49" s="5"/>
       <c r="AB49" s="5"/>
@@ -3443,33 +3672,33 @@
       <c r="AF49" s="5"/>
     </row>
     <row r="50" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A50" s="43" t="s">
-        <v>107</v>
-      </c>
-      <c r="B50" s="38"/>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="39"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="38"/>
-      <c r="K50" s="38"/>
-      <c r="L50" s="38"/>
-      <c r="M50" s="38"/>
-      <c r="N50" s="38"/>
-      <c r="O50" s="38"/>
-      <c r="P50" s="38"/>
-      <c r="Q50" s="38"/>
-      <c r="R50" s="38"/>
-      <c r="S50" s="38"/>
-      <c r="T50" s="38"/>
-      <c r="U50" s="38"/>
-      <c r="V50" s="38"/>
-      <c r="W50" s="38"/>
-      <c r="X50" s="5"/>
-      <c r="Y50" s="5"/>
+      <c r="A50" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="B50" s="63"/>
+      <c r="C50" s="63"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="63"/>
+      <c r="J50" s="63"/>
+      <c r="K50" s="63"/>
+      <c r="L50" s="63"/>
+      <c r="M50" s="63"/>
+      <c r="N50" s="63"/>
+      <c r="O50" s="63"/>
+      <c r="P50" s="63"/>
+      <c r="Q50" s="63"/>
+      <c r="R50" s="63"/>
+      <c r="S50" s="63"/>
+      <c r="T50" s="63"/>
+      <c r="U50" s="63"/>
+      <c r="V50" s="63"/>
+      <c r="W50" s="63"/>
+      <c r="X50" s="19"/>
+      <c r="Y50" s="38"/>
       <c r="Z50" s="5"/>
       <c r="AA50" s="5"/>
       <c r="AB50" s="5"/>
@@ -3480,24 +3709,24 @@
     </row>
     <row r="51" spans="1:32" ht="18" customHeight="1">
       <c r="A51" s="24" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D51" s="20"/>
       <c r="E51" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="G51" s="19"/>
       <c r="H51" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I51" s="19"/>
       <c r="J51" s="19"/>
@@ -3514,8 +3743,10 @@
       <c r="U51" s="19"/>
       <c r="V51" s="19"/>
       <c r="W51" s="19"/>
-      <c r="X51" s="5"/>
-      <c r="Y51" s="5"/>
+      <c r="X51" s="19"/>
+      <c r="Y51" s="38" t="s">
+        <v>134</v>
+      </c>
       <c r="Z51" s="5"/>
       <c r="AA51" s="5"/>
       <c r="AB51" s="5"/>
@@ -3526,22 +3757,22 @@
     </row>
     <row r="52" spans="1:32" ht="18" customHeight="1">
       <c r="A52" s="24" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D52" s="15"/>
       <c r="E52" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F52" s="17"/>
       <c r="G52" s="19"/>
       <c r="H52" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I52" s="19"/>
       <c r="J52" s="19"/>
@@ -3558,8 +3789,10 @@
       <c r="U52" s="19"/>
       <c r="V52" s="19"/>
       <c r="W52" s="19"/>
-      <c r="X52" s="5"/>
-      <c r="Y52" s="5"/>
+      <c r="X52" s="19"/>
+      <c r="Y52" s="38" t="s">
+        <v>134</v>
+      </c>
       <c r="Z52" s="5"/>
       <c r="AA52" s="5"/>
       <c r="AB52" s="5"/>
@@ -3569,160 +3802,178 @@
       <c r="AF52" s="5"/>
     </row>
     <row r="53" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A53" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="B53" s="38"/>
-      <c r="C53" s="38"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="39"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="38"/>
-      <c r="I53" s="38"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
-      <c r="L53" s="38"/>
-      <c r="M53" s="38"/>
-      <c r="N53" s="38"/>
-      <c r="O53" s="38"/>
-      <c r="P53" s="38"/>
-      <c r="Q53" s="38"/>
-      <c r="R53" s="38"/>
-      <c r="S53" s="38"/>
-      <c r="T53" s="38"/>
-      <c r="U53" s="38"/>
-      <c r="V53" s="38"/>
-      <c r="W53" s="38"/>
-    </row>
-    <row r="54" spans="1:32" ht="24" customHeight="1">
+      <c r="A53" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="B53" s="63"/>
+      <c r="C53" s="63"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="63"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="63"/>
+      <c r="H53" s="63"/>
+      <c r="I53" s="63"/>
+      <c r="J53" s="63"/>
+      <c r="K53" s="63"/>
+      <c r="L53" s="63"/>
+      <c r="M53" s="63"/>
+      <c r="N53" s="63"/>
+      <c r="O53" s="63"/>
+      <c r="P53" s="63"/>
+      <c r="Q53" s="63"/>
+      <c r="R53" s="63"/>
+      <c r="S53" s="63"/>
+      <c r="T53" s="63"/>
+      <c r="U53" s="63"/>
+      <c r="V53" s="63"/>
+      <c r="W53" s="63"/>
+    </row>
+    <row r="54" spans="1:32" ht="48.75" customHeight="1">
       <c r="A54" s="15" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="G54" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="X54" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y54" s="39" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:32" ht="24" customHeight="1">
       <c r="A55" s="15" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="X55" s="40" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:32" ht="24" customHeight="1">
       <c r="A56" s="15" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F56" s="17" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="I56" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="X56" s="40" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:32" ht="24" customHeight="1">
       <c r="A57" s="15" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="I57" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="X57" s="40" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:32" ht="18" customHeight="1">
       <c r="A58" s="15" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="B58" s="25" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="J58" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="X58" s="40" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A59" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="B59" s="38"/>
-      <c r="C59" s="38"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="39"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38"/>
-      <c r="J59" s="38"/>
-      <c r="K59" s="38"/>
-      <c r="L59" s="38"/>
-      <c r="M59" s="38"/>
-      <c r="N59" s="38"/>
-      <c r="O59" s="38"/>
-      <c r="P59" s="38"/>
-      <c r="Q59" s="38"/>
-      <c r="R59" s="38"/>
-      <c r="S59" s="38"/>
-      <c r="T59" s="38"/>
-      <c r="U59" s="38"/>
-      <c r="V59" s="38"/>
-      <c r="W59" s="38"/>
-      <c r="X59" s="5"/>
-      <c r="Y59" s="5"/>
+      <c r="A59" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="B59" s="63"/>
+      <c r="C59" s="63"/>
+      <c r="D59" s="63"/>
+      <c r="E59" s="63"/>
+      <c r="F59" s="43"/>
+      <c r="G59" s="63"/>
+      <c r="H59" s="63"/>
+      <c r="I59" s="63"/>
+      <c r="J59" s="63"/>
+      <c r="K59" s="63"/>
+      <c r="L59" s="63"/>
+      <c r="M59" s="63"/>
+      <c r="N59" s="63"/>
+      <c r="O59" s="63"/>
+      <c r="P59" s="63"/>
+      <c r="Q59" s="63"/>
+      <c r="R59" s="63"/>
+      <c r="S59" s="63"/>
+      <c r="T59" s="63"/>
+      <c r="U59" s="63"/>
+      <c r="V59" s="63"/>
+      <c r="W59" s="63"/>
+      <c r="X59" s="19"/>
+      <c r="Y59" s="38"/>
       <c r="Z59" s="5"/>
       <c r="AA59" s="5"/>
       <c r="AB59" s="5"/>
@@ -3731,29 +3982,29 @@
       <c r="AE59" s="5"/>
       <c r="AF59" s="5"/>
     </row>
-    <row r="60" spans="1:32" ht="18" customHeight="1">
+    <row r="60" spans="1:32" ht="40.5" customHeight="1">
       <c r="A60" s="13" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D60" s="20"/>
       <c r="E60" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F60" s="17" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="G60" s="19"/>
       <c r="H60" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I60" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J60" s="19"/>
       <c r="K60" s="19"/>
@@ -3769,8 +4020,12 @@
       <c r="U60" s="19"/>
       <c r="V60" s="19"/>
       <c r="W60" s="19"/>
-      <c r="X60" s="5"/>
-      <c r="Y60" s="5"/>
+      <c r="X60" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y60" s="38" t="s">
+        <v>156</v>
+      </c>
       <c r="Z60" s="5"/>
       <c r="AA60" s="5"/>
       <c r="AB60" s="5"/>
@@ -3781,25 +4036,27 @@
     </row>
     <row r="61" spans="1:32" ht="18" customHeight="1">
       <c r="A61" s="13" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B61" s="25" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="X61" s="5"/>
-      <c r="Y61" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="X61" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y61" s="38"/>
       <c r="Z61" s="5"/>
       <c r="AA61" s="5"/>
       <c r="AB61" s="5"/>
@@ -3810,17 +4067,17 @@
     </row>
     <row r="62" spans="1:32" ht="18" customHeight="1">
       <c r="A62" s="13" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D62" s="20"/>
       <c r="E62" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F62" s="17"/>
       <c r="G62" s="19"/>
@@ -3828,7 +4085,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="19"/>
       <c r="K62" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L62" s="19"/>
       <c r="M62" s="19"/>
@@ -3842,8 +4099,10 @@
       <c r="U62" s="19"/>
       <c r="V62" s="19"/>
       <c r="W62" s="19"/>
-      <c r="X62" s="5"/>
-      <c r="Y62" s="5"/>
+      <c r="X62" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y62" s="38"/>
       <c r="Z62" s="5"/>
       <c r="AA62" s="5"/>
       <c r="AB62" s="5"/>
@@ -3854,20 +4113,20 @@
     </row>
     <row r="63" spans="1:32" ht="18" customHeight="1">
       <c r="A63" s="13" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D63" s="20"/>
       <c r="E63" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="G63" s="19"/>
       <c r="H63" s="19"/>
@@ -3875,7 +4134,7 @@
       <c r="J63" s="19"/>
       <c r="K63" s="19"/>
       <c r="L63" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M63" s="19"/>
       <c r="N63" s="19"/>
@@ -3888,8 +4147,10 @@
       <c r="U63" s="19"/>
       <c r="V63" s="19"/>
       <c r="W63" s="19"/>
-      <c r="X63" s="5"/>
-      <c r="Y63" s="5"/>
+      <c r="X63" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y63" s="38"/>
       <c r="Z63" s="5"/>
       <c r="AA63" s="5"/>
       <c r="AB63" s="5"/>
@@ -3900,20 +4161,20 @@
     </row>
     <row r="64" spans="1:32" ht="18" customHeight="1">
       <c r="A64" s="13" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="D64" s="15"/>
       <c r="E64" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="G64" s="19"/>
       <c r="H64" s="19"/>
@@ -3921,10 +4182,10 @@
       <c r="J64" s="19"/>
       <c r="K64" s="19"/>
       <c r="L64" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M64" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N64" s="19"/>
       <c r="O64" s="19"/>
@@ -3936,8 +4197,10 @@
       <c r="U64" s="19"/>
       <c r="V64" s="19"/>
       <c r="W64" s="19"/>
-      <c r="X64" s="5"/>
-      <c r="Y64" s="5"/>
+      <c r="X64" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y64" s="38"/>
       <c r="Z64" s="5"/>
       <c r="AA64" s="5"/>
       <c r="AB64" s="5"/>
@@ -3948,20 +4211,20 @@
     </row>
     <row r="65" spans="1:32" ht="18" customHeight="1">
       <c r="A65" s="13" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="D65" s="20"/>
       <c r="E65" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="G65" s="19"/>
       <c r="H65" s="19"/>
@@ -3971,7 +4234,7 @@
       <c r="L65" s="19"/>
       <c r="M65" s="19"/>
       <c r="N65" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O65" s="19"/>
       <c r="P65" s="19"/>
@@ -3982,8 +4245,10 @@
       <c r="U65" s="19"/>
       <c r="V65" s="19"/>
       <c r="W65" s="19"/>
-      <c r="X65" s="5"/>
-      <c r="Y65" s="5"/>
+      <c r="X65" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y65" s="38"/>
       <c r="Z65" s="5"/>
       <c r="AA65" s="5"/>
       <c r="AB65" s="5"/>
@@ -3994,20 +4259,20 @@
     </row>
     <row r="66" spans="1:32" ht="15" customHeight="1">
       <c r="A66" s="13" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="D66" s="20"/>
       <c r="E66" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="G66" s="19"/>
       <c r="H66" s="19"/>
@@ -4017,7 +4282,7 @@
       <c r="L66" s="19"/>
       <c r="M66" s="19"/>
       <c r="N66" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O66" s="19"/>
       <c r="P66" s="19"/>
@@ -4028,8 +4293,8 @@
       <c r="U66" s="19"/>
       <c r="V66" s="19"/>
       <c r="W66" s="19"/>
-      <c r="X66" s="5"/>
-      <c r="Y66" s="5"/>
+      <c r="X66" s="19"/>
+      <c r="Y66" s="38"/>
       <c r="Z66" s="5"/>
       <c r="AA66" s="5"/>
       <c r="AB66" s="5"/>
@@ -4039,33 +4304,33 @@
       <c r="AF66" s="5"/>
     </row>
     <row r="67" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A67" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="B67" s="38"/>
-      <c r="C67" s="38"/>
-      <c r="D67" s="38"/>
-      <c r="E67" s="38"/>
-      <c r="F67" s="39"/>
-      <c r="G67" s="38"/>
-      <c r="H67" s="38"/>
-      <c r="I67" s="38"/>
-      <c r="J67" s="38"/>
-      <c r="K67" s="38"/>
-      <c r="L67" s="38"/>
-      <c r="M67" s="38"/>
-      <c r="N67" s="38"/>
-      <c r="O67" s="38"/>
-      <c r="P67" s="38"/>
-      <c r="Q67" s="38"/>
-      <c r="R67" s="38"/>
-      <c r="S67" s="38"/>
-      <c r="T67" s="38"/>
-      <c r="U67" s="38"/>
-      <c r="V67" s="38"/>
-      <c r="W67" s="38"/>
-      <c r="X67" s="5"/>
-      <c r="Y67" s="5"/>
+      <c r="A67" s="55" t="s">
+        <v>171</v>
+      </c>
+      <c r="B67" s="63"/>
+      <c r="C67" s="63"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="63"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="63"/>
+      <c r="H67" s="63"/>
+      <c r="I67" s="63"/>
+      <c r="J67" s="63"/>
+      <c r="K67" s="63"/>
+      <c r="L67" s="63"/>
+      <c r="M67" s="63"/>
+      <c r="N67" s="63"/>
+      <c r="O67" s="63"/>
+      <c r="P67" s="63"/>
+      <c r="Q67" s="63"/>
+      <c r="R67" s="63"/>
+      <c r="S67" s="63"/>
+      <c r="T67" s="63"/>
+      <c r="U67" s="63"/>
+      <c r="V67" s="63"/>
+      <c r="W67" s="63"/>
+      <c r="X67" s="19"/>
+      <c r="Y67" s="38"/>
       <c r="Z67" s="5"/>
       <c r="AA67" s="5"/>
       <c r="AB67" s="5"/>
@@ -4074,25 +4339,29 @@
       <c r="AE67" s="5"/>
       <c r="AF67" s="5"/>
     </row>
-    <row r="68" spans="1:32" ht="18" customHeight="1">
+    <row r="68" spans="1:32" ht="42" customHeight="1">
       <c r="A68" s="24" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F68" s="26"/>
       <c r="P68" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="X68" s="5"/>
-      <c r="Y68" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="X68" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y68" s="38" t="s">
+        <v>175</v>
+      </c>
       <c r="Z68" s="5"/>
       <c r="AA68" s="5"/>
       <c r="AB68" s="5"/>
@@ -4103,17 +4372,17 @@
     </row>
     <row r="69" spans="1:32" ht="18" customHeight="1">
       <c r="A69" s="24" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="D69" s="20"/>
       <c r="E69" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F69" s="17"/>
       <c r="G69" s="19"/>
@@ -4127,7 +4396,7 @@
       <c r="O69" s="19"/>
       <c r="P69" s="19"/>
       <c r="Q69" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R69" s="19"/>
       <c r="S69" s="19"/>
@@ -4135,8 +4404,10 @@
       <c r="U69" s="19"/>
       <c r="V69" s="19"/>
       <c r="W69" s="19"/>
-      <c r="X69" s="5"/>
-      <c r="Y69" s="5"/>
+      <c r="X69" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y69" s="38"/>
       <c r="Z69" s="5"/>
       <c r="AA69" s="5"/>
       <c r="AB69" s="5"/>
@@ -4147,17 +4418,17 @@
     </row>
     <row r="70" spans="1:32" ht="18" customHeight="1">
       <c r="A70" s="24" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D70" s="15"/>
       <c r="E70" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F70" s="17"/>
       <c r="G70" s="19"/>
@@ -4172,15 +4443,17 @@
       <c r="P70" s="19"/>
       <c r="Q70" s="19"/>
       <c r="R70" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="S70" s="19"/>
       <c r="T70" s="19"/>
       <c r="U70" s="19"/>
       <c r="V70" s="19"/>
       <c r="W70" s="19"/>
-      <c r="X70" s="5"/>
-      <c r="Y70" s="5"/>
+      <c r="X70" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y70" s="38"/>
       <c r="Z70" s="5"/>
       <c r="AA70" s="5"/>
       <c r="AB70" s="5"/>
@@ -4191,17 +4464,17 @@
     </row>
     <row r="71" spans="1:32" ht="18" customHeight="1">
       <c r="A71" s="24" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="D71" s="20"/>
       <c r="E71" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F71" s="17"/>
       <c r="G71" s="19"/>
@@ -4217,16 +4490,18 @@
       <c r="Q71" s="19"/>
       <c r="R71" s="19"/>
       <c r="S71" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="T71" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="U71" s="19"/>
       <c r="V71" s="19"/>
       <c r="W71" s="19"/>
-      <c r="X71" s="5"/>
-      <c r="Y71" s="5"/>
+      <c r="X71" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y71" s="38"/>
       <c r="Z71" s="5"/>
       <c r="AA71" s="5"/>
       <c r="AB71" s="5"/>
@@ -4237,474 +4512,486 @@
     </row>
     <row r="72" spans="1:32" ht="18" customHeight="1"/>
     <row r="73" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A73" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="B73" s="38"/>
-      <c r="C73" s="38"/>
-      <c r="D73" s="38"/>
-      <c r="E73" s="38"/>
-      <c r="F73" s="39"/>
-      <c r="G73" s="38"/>
-      <c r="H73" s="38"/>
-      <c r="I73" s="38"/>
-      <c r="J73" s="38"/>
-      <c r="K73" s="38"/>
-      <c r="L73" s="38"/>
-      <c r="M73" s="38"/>
-      <c r="N73" s="38"/>
-      <c r="O73" s="38"/>
-      <c r="P73" s="38"/>
-      <c r="Q73" s="38"/>
-      <c r="R73" s="38"/>
-      <c r="S73" s="38"/>
-      <c r="T73" s="38"/>
-      <c r="U73" s="38"/>
-      <c r="V73" s="38"/>
-      <c r="W73" s="38"/>
+      <c r="A73" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="B73" s="63"/>
+      <c r="C73" s="63"/>
+      <c r="D73" s="63"/>
+      <c r="E73" s="63"/>
+      <c r="F73" s="43"/>
+      <c r="G73" s="63"/>
+      <c r="H73" s="63"/>
+      <c r="I73" s="63"/>
+      <c r="J73" s="63"/>
+      <c r="K73" s="63"/>
+      <c r="L73" s="63"/>
+      <c r="M73" s="63"/>
+      <c r="N73" s="63"/>
+      <c r="O73" s="63"/>
+      <c r="P73" s="63"/>
+      <c r="Q73" s="63"/>
+      <c r="R73" s="63"/>
+      <c r="S73" s="63"/>
+      <c r="T73" s="63"/>
+      <c r="U73" s="63"/>
+      <c r="V73" s="63"/>
+      <c r="W73" s="63"/>
     </row>
     <row r="74" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A74" s="50" t="s">
-        <v>151</v>
-      </c>
-      <c r="B74" s="38"/>
-      <c r="C74" s="38"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="39"/>
-      <c r="G74" s="38"/>
-      <c r="H74" s="38"/>
-      <c r="I74" s="38"/>
-      <c r="J74" s="38"/>
-      <c r="K74" s="38"/>
-      <c r="L74" s="38"/>
-      <c r="M74" s="38"/>
-      <c r="N74" s="38"/>
-      <c r="O74" s="38"/>
-      <c r="P74" s="38"/>
-      <c r="Q74" s="38"/>
-      <c r="R74" s="38"/>
-      <c r="S74" s="38"/>
-      <c r="T74" s="38"/>
-      <c r="U74" s="38"/>
-      <c r="V74" s="38"/>
-      <c r="W74" s="38"/>
+      <c r="A74" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="B74" s="63"/>
+      <c r="C74" s="63"/>
+      <c r="D74" s="63"/>
+      <c r="E74" s="63"/>
+      <c r="F74" s="43"/>
+      <c r="G74" s="63"/>
+      <c r="H74" s="63"/>
+      <c r="I74" s="63"/>
+      <c r="J74" s="63"/>
+      <c r="K74" s="63"/>
+      <c r="L74" s="63"/>
+      <c r="M74" s="63"/>
+      <c r="N74" s="63"/>
+      <c r="O74" s="63"/>
+      <c r="P74" s="63"/>
+      <c r="Q74" s="63"/>
+      <c r="R74" s="63"/>
+      <c r="S74" s="63"/>
+      <c r="T74" s="63"/>
+      <c r="U74" s="63"/>
+      <c r="V74" s="63"/>
+      <c r="W74" s="63"/>
     </row>
     <row r="75" spans="1:32" ht="36" customHeight="1">
       <c r="A75" s="16" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D75" s="15"/>
       <c r="E75" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="G75" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="76" spans="1:32" ht="36" customHeight="1">
       <c r="A76" s="16" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="D76" s="15"/>
       <c r="E76" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="G76" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77" spans="1:32" ht="24" customHeight="1">
       <c r="A77" s="16" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="D77" s="15"/>
       <c r="E77" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="G77" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:32" ht="24" customHeight="1">
       <c r="A78" s="16" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D78" s="15"/>
       <c r="E78" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="G78" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A79" s="50" t="s">
-        <v>163</v>
-      </c>
-      <c r="B79" s="38"/>
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="39"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38"/>
-      <c r="J79" s="38"/>
-      <c r="K79" s="38"/>
-      <c r="L79" s="38"/>
-      <c r="M79" s="38"/>
-      <c r="N79" s="38"/>
-      <c r="O79" s="38"/>
-      <c r="P79" s="38"/>
-      <c r="Q79" s="38"/>
-      <c r="R79" s="38"/>
-      <c r="S79" s="38"/>
-      <c r="T79" s="38"/>
-      <c r="U79" s="38"/>
-      <c r="V79" s="38"/>
-      <c r="W79" s="38"/>
+      <c r="A79" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="B79" s="63"/>
+      <c r="C79" s="63"/>
+      <c r="D79" s="63"/>
+      <c r="E79" s="63"/>
+      <c r="F79" s="43"/>
+      <c r="G79" s="63"/>
+      <c r="H79" s="63"/>
+      <c r="I79" s="63"/>
+      <c r="J79" s="63"/>
+      <c r="K79" s="63"/>
+      <c r="L79" s="63"/>
+      <c r="M79" s="63"/>
+      <c r="N79" s="63"/>
+      <c r="O79" s="63"/>
+      <c r="P79" s="63"/>
+      <c r="Q79" s="63"/>
+      <c r="R79" s="63"/>
+      <c r="S79" s="63"/>
+      <c r="T79" s="63"/>
+      <c r="U79" s="63"/>
+      <c r="V79" s="63"/>
+      <c r="W79" s="63"/>
     </row>
     <row r="80" spans="1:32" ht="36" customHeight="1">
       <c r="A80" s="16" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="D80" s="15"/>
       <c r="E80" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F80" s="17" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="H80" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="X80" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y80" s="39" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="81" spans="1:32" ht="36" customHeight="1">
       <c r="A81" s="16" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D81" s="15"/>
       <c r="E81" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="H81" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:32" ht="24" customHeight="1">
       <c r="A82" s="16" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="D82" s="15"/>
       <c r="E82" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F82" s="17" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="H82" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="X82" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y82" s="39" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="83" spans="1:32" ht="24" customHeight="1">
       <c r="A83" s="16" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D83" s="15"/>
       <c r="E83" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F83" s="17" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="H83" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="84" spans="1:32" ht="36" customHeight="1">
       <c r="A84" s="16" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D84" s="15"/>
       <c r="E84" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F84" s="17" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="H84" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="85" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A85" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="B85" s="38"/>
-      <c r="C85" s="38"/>
-      <c r="D85" s="38"/>
-      <c r="E85" s="38"/>
-      <c r="F85" s="39"/>
-      <c r="G85" s="38"/>
-      <c r="H85" s="38"/>
-      <c r="I85" s="38"/>
-      <c r="J85" s="38"/>
-      <c r="K85" s="38"/>
-      <c r="L85" s="38"/>
-      <c r="M85" s="38"/>
-      <c r="N85" s="38"/>
-      <c r="O85" s="38"/>
-      <c r="P85" s="38"/>
-      <c r="Q85" s="38"/>
-      <c r="R85" s="38"/>
-      <c r="S85" s="38"/>
-      <c r="T85" s="38"/>
-      <c r="U85" s="38"/>
-      <c r="V85" s="38"/>
-      <c r="W85" s="38"/>
+      <c r="A85" s="46" t="s">
+        <v>208</v>
+      </c>
+      <c r="B85" s="63"/>
+      <c r="C85" s="63"/>
+      <c r="D85" s="63"/>
+      <c r="E85" s="63"/>
+      <c r="F85" s="43"/>
+      <c r="G85" s="63"/>
+      <c r="H85" s="63"/>
+      <c r="I85" s="63"/>
+      <c r="J85" s="63"/>
+      <c r="K85" s="63"/>
+      <c r="L85" s="63"/>
+      <c r="M85" s="63"/>
+      <c r="N85" s="63"/>
+      <c r="O85" s="63"/>
+      <c r="P85" s="63"/>
+      <c r="Q85" s="63"/>
+      <c r="R85" s="63"/>
+      <c r="S85" s="63"/>
+      <c r="T85" s="63"/>
+      <c r="U85" s="63"/>
+      <c r="V85" s="63"/>
+      <c r="W85" s="63"/>
     </row>
     <row r="86" spans="1:32" ht="24" customHeight="1">
       <c r="A86" s="16" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="D86" s="15"/>
       <c r="E86" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F86" s="17" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="I86" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="87" spans="1:32" ht="36" customHeight="1">
       <c r="A87" s="16" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D87" s="15"/>
       <c r="E87" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F87" s="17" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="I87" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="88" spans="1:32" ht="36" customHeight="1">
       <c r="A88" s="16" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="D88" s="15"/>
       <c r="E88" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F88" s="17" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="I88" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="89" spans="1:32" ht="36" customHeight="1">
       <c r="A89" s="16" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="D89" s="15"/>
       <c r="E89" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F89" s="17" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="I89" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:32" ht="19.5" customHeight="1">
-      <c r="A90" s="50" t="s">
-        <v>187</v>
-      </c>
-      <c r="B90" s="38"/>
-      <c r="C90" s="38"/>
-      <c r="D90" s="38"/>
-      <c r="E90" s="38"/>
-      <c r="F90" s="39"/>
-      <c r="G90" s="38"/>
-      <c r="H90" s="38"/>
-      <c r="I90" s="38"/>
-      <c r="J90" s="38"/>
-      <c r="K90" s="38"/>
-      <c r="L90" s="38"/>
-      <c r="M90" s="38"/>
-      <c r="N90" s="38"/>
-      <c r="O90" s="38"/>
-      <c r="P90" s="38"/>
-      <c r="Q90" s="38"/>
-      <c r="R90" s="38"/>
-      <c r="S90" s="38"/>
-      <c r="T90" s="38"/>
-      <c r="U90" s="38"/>
-      <c r="V90" s="38"/>
-      <c r="W90" s="38"/>
+      <c r="A90" s="46" t="s">
+        <v>219</v>
+      </c>
+      <c r="B90" s="63"/>
+      <c r="C90" s="63"/>
+      <c r="D90" s="63"/>
+      <c r="E90" s="63"/>
+      <c r="F90" s="43"/>
+      <c r="G90" s="63"/>
+      <c r="H90" s="63"/>
+      <c r="I90" s="63"/>
+      <c r="J90" s="63"/>
+      <c r="K90" s="63"/>
+      <c r="L90" s="63"/>
+      <c r="M90" s="63"/>
+      <c r="N90" s="63"/>
+      <c r="O90" s="63"/>
+      <c r="P90" s="63"/>
+      <c r="Q90" s="63"/>
+      <c r="R90" s="63"/>
+      <c r="S90" s="63"/>
+      <c r="T90" s="63"/>
+      <c r="U90" s="63"/>
+      <c r="V90" s="63"/>
+      <c r="W90" s="63"/>
     </row>
     <row r="91" spans="1:32" ht="24" customHeight="1">
       <c r="A91" s="16" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D91" s="15"/>
       <c r="E91" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F91" s="17" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="J91" s="27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="92" spans="1:32" ht="36" customHeight="1">
       <c r="A92" s="16" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D92" s="15"/>
       <c r="E92" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F92" s="17" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="J92" s="27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="93" spans="1:32" ht="36" customHeight="1">
       <c r="A93" s="15" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="D93" s="15"/>
       <c r="E93" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F93" s="17" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="J93" s="27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="94" spans="1:32" ht="12" customHeight="1">
@@ -4717,33 +5004,33 @@
       <c r="J94" s="27"/>
     </row>
     <row r="95" spans="1:32" ht="16.5" customHeight="1">
-      <c r="A95" s="56" t="s">
-        <v>197</v>
-      </c>
-      <c r="B95" s="38"/>
-      <c r="C95" s="38"/>
-      <c r="D95" s="38"/>
-      <c r="E95" s="38"/>
-      <c r="F95" s="39"/>
-      <c r="G95" s="38"/>
-      <c r="H95" s="38"/>
-      <c r="I95" s="38"/>
-      <c r="J95" s="38"/>
-      <c r="K95" s="38"/>
-      <c r="L95" s="38"/>
-      <c r="M95" s="38"/>
-      <c r="N95" s="38"/>
-      <c r="O95" s="38"/>
-      <c r="P95" s="38"/>
-      <c r="Q95" s="38"/>
-      <c r="R95" s="38"/>
-      <c r="S95" s="38"/>
-      <c r="T95" s="38"/>
-      <c r="U95" s="38"/>
-      <c r="V95" s="38"/>
-      <c r="W95" s="38"/>
-      <c r="X95" s="5"/>
-      <c r="Y95" s="5"/>
+      <c r="A95" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="B95" s="63"/>
+      <c r="C95" s="63"/>
+      <c r="D95" s="63"/>
+      <c r="E95" s="63"/>
+      <c r="F95" s="43"/>
+      <c r="G95" s="63"/>
+      <c r="H95" s="63"/>
+      <c r="I95" s="63"/>
+      <c r="J95" s="63"/>
+      <c r="K95" s="63"/>
+      <c r="L95" s="63"/>
+      <c r="M95" s="63"/>
+      <c r="N95" s="63"/>
+      <c r="O95" s="63"/>
+      <c r="P95" s="63"/>
+      <c r="Q95" s="63"/>
+      <c r="R95" s="63"/>
+      <c r="S95" s="63"/>
+      <c r="T95" s="63"/>
+      <c r="U95" s="63"/>
+      <c r="V95" s="63"/>
+      <c r="W95" s="63"/>
+      <c r="X95" s="19"/>
+      <c r="Y95" s="38"/>
       <c r="Z95" s="5"/>
       <c r="AA95" s="5"/>
       <c r="AB95" s="5"/>
@@ -4754,11 +5041,11 @@
     </row>
     <row r="96" spans="1:32" ht="15.75" customHeight="1">
       <c r="A96" s="28" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="F96" s="2"/>
-      <c r="X96" s="5"/>
-      <c r="Y96" s="5"/>
+      <c r="X96" s="19"/>
+      <c r="Y96" s="38"/>
       <c r="Z96" s="5"/>
       <c r="AA96" s="5"/>
       <c r="AB96" s="5"/>
@@ -4769,26 +5056,26 @@
     </row>
     <row r="97" spans="1:32" ht="24" customHeight="1">
       <c r="A97" s="29" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="C97" s="31" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="D97" s="31"/>
       <c r="E97" s="32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G97" s="19"/>
       <c r="H97" s="19"/>
       <c r="I97" s="19"/>
       <c r="J97" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K97" s="19"/>
       <c r="L97" s="19"/>
@@ -4803,8 +5090,8 @@
       <c r="U97" s="19"/>
       <c r="V97" s="19"/>
       <c r="W97" s="19"/>
-      <c r="X97" s="5"/>
-      <c r="Y97" s="5"/>
+      <c r="X97" s="19"/>
+      <c r="Y97" s="38"/>
       <c r="Z97" s="5"/>
       <c r="AA97" s="5"/>
       <c r="AB97" s="5"/>
@@ -4815,20 +5102,20 @@
     </row>
     <row r="98" spans="1:32" ht="24" customHeight="1">
       <c r="A98" s="29" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="B98" s="30" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="C98" s="34" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D98" s="34"/>
       <c r="E98" s="32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G98" s="19"/>
       <c r="H98" s="19"/>
@@ -4838,7 +5125,7 @@
       <c r="L98" s="19"/>
       <c r="M98" s="19"/>
       <c r="N98" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O98" s="19"/>
       <c r="P98" s="19"/>
@@ -4849,8 +5136,8 @@
       <c r="U98" s="19"/>
       <c r="V98" s="19"/>
       <c r="W98" s="19"/>
-      <c r="X98" s="5"/>
-      <c r="Y98" s="5"/>
+      <c r="X98" s="19"/>
+      <c r="Y98" s="38"/>
       <c r="Z98" s="5"/>
       <c r="AA98" s="5"/>
       <c r="AB98" s="5"/>
@@ -4861,20 +5148,20 @@
     </row>
     <row r="99" spans="1:32" ht="24" customHeight="1">
       <c r="A99" s="29" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="B99" s="30" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="C99" s="34" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="D99" s="34"/>
       <c r="E99" s="32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G99" s="19"/>
       <c r="H99" s="19"/>
@@ -4888,15 +5175,15 @@
       <c r="P99" s="19"/>
       <c r="Q99" s="19"/>
       <c r="R99" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="S99" s="19"/>
       <c r="T99" s="19"/>
       <c r="U99" s="19"/>
       <c r="V99" s="19"/>
       <c r="W99" s="19"/>
-      <c r="X99" s="5"/>
-      <c r="Y99" s="5"/>
+      <c r="X99" s="19"/>
+      <c r="Y99" s="38"/>
       <c r="Z99" s="5"/>
       <c r="AA99" s="5"/>
       <c r="AB99" s="5"/>
@@ -4907,20 +5194,20 @@
     </row>
     <row r="100" spans="1:32" ht="24" customHeight="1">
       <c r="A100" s="29" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="D100" s="31"/>
       <c r="E100" s="32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G100" s="19"/>
       <c r="H100" s="19"/>
@@ -4939,10 +5226,10 @@
       <c r="U100" s="19"/>
       <c r="V100" s="19"/>
       <c r="W100" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="X100" s="5"/>
-      <c r="Y100" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="X100" s="19"/>
+      <c r="Y100" s="38"/>
       <c r="Z100" s="5"/>
       <c r="AA100" s="5"/>
       <c r="AB100" s="5"/>
@@ -4953,11 +5240,11 @@
     </row>
     <row r="101" spans="1:32" ht="16.5" customHeight="1">
       <c r="A101" s="28" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="F101" s="2"/>
-      <c r="X101" s="5"/>
-      <c r="Y101" s="5"/>
+      <c r="X101" s="19"/>
+      <c r="Y101" s="38"/>
       <c r="Z101" s="5"/>
       <c r="AA101" s="5"/>
       <c r="AB101" s="5"/>
@@ -4990,8 +5277,8 @@
       <c r="U102" s="5"/>
       <c r="V102" s="5"/>
       <c r="W102" s="5"/>
-      <c r="X102" s="5"/>
-      <c r="Y102" s="5"/>
+      <c r="X102" s="19"/>
+      <c r="Y102" s="38"/>
       <c r="Z102" s="5"/>
       <c r="AA102" s="5"/>
       <c r="AB102" s="5"/>
@@ -5001,31 +5288,31 @@
       <c r="AF102" s="5"/>
     </row>
     <row r="103" spans="1:32" ht="15.75" customHeight="1">
-      <c r="A103" s="49" t="s">
-        <v>209</v>
-      </c>
-      <c r="B103" s="38"/>
-      <c r="C103" s="38"/>
-      <c r="D103" s="38"/>
-      <c r="E103" s="38"/>
-      <c r="F103" s="39"/>
-      <c r="G103" s="38"/>
-      <c r="H103" s="38"/>
-      <c r="I103" s="38"/>
-      <c r="J103" s="38"/>
-      <c r="K103" s="38"/>
-      <c r="L103" s="38"/>
-      <c r="M103" s="38"/>
-      <c r="N103" s="38"/>
-      <c r="O103" s="38"/>
-      <c r="P103" s="38"/>
-      <c r="Q103" s="38"/>
-      <c r="R103" s="38"/>
-      <c r="S103" s="38"/>
-      <c r="T103" s="38"/>
-      <c r="U103" s="38"/>
-      <c r="V103" s="38"/>
-      <c r="W103" s="38"/>
+      <c r="A103" s="45" t="s">
+        <v>241</v>
+      </c>
+      <c r="B103" s="63"/>
+      <c r="C103" s="63"/>
+      <c r="D103" s="63"/>
+      <c r="E103" s="63"/>
+      <c r="F103" s="43"/>
+      <c r="G103" s="63"/>
+      <c r="H103" s="63"/>
+      <c r="I103" s="63"/>
+      <c r="J103" s="63"/>
+      <c r="K103" s="63"/>
+      <c r="L103" s="63"/>
+      <c r="M103" s="63"/>
+      <c r="N103" s="63"/>
+      <c r="O103" s="63"/>
+      <c r="P103" s="63"/>
+      <c r="Q103" s="63"/>
+      <c r="R103" s="63"/>
+      <c r="S103" s="63"/>
+      <c r="T103" s="63"/>
+      <c r="U103" s="63"/>
+      <c r="V103" s="63"/>
+      <c r="W103" s="63"/>
     </row>
     <row r="104" spans="1:32" ht="15.75" customHeight="1">
       <c r="A104" s="35"/>
@@ -5051,8 +5338,8 @@
       <c r="U104" s="5"/>
       <c r="V104" s="5"/>
       <c r="W104" s="5"/>
-      <c r="X104" s="5"/>
-      <c r="Y104" s="5"/>
+      <c r="X104" s="19"/>
+      <c r="Y104" s="38"/>
       <c r="Z104" s="5"/>
       <c r="AA104" s="5"/>
       <c r="AB104" s="5"/>
@@ -5085,8 +5372,8 @@
       <c r="U105" s="5"/>
       <c r="V105" s="5"/>
       <c r="W105" s="5"/>
-      <c r="X105" s="5"/>
-      <c r="Y105" s="5"/>
+      <c r="X105" s="19"/>
+      <c r="Y105" s="38"/>
       <c r="Z105" s="5"/>
       <c r="AA105" s="5"/>
       <c r="AB105" s="5"/>
@@ -5119,8 +5406,8 @@
       <c r="U106" s="5"/>
       <c r="V106" s="5"/>
       <c r="W106" s="5"/>
-      <c r="X106" s="5"/>
-      <c r="Y106" s="5"/>
+      <c r="X106" s="19"/>
+      <c r="Y106" s="38"/>
       <c r="Z106" s="5"/>
       <c r="AA106" s="5"/>
       <c r="AB106" s="5"/>
@@ -5153,8 +5440,8 @@
       <c r="U107" s="5"/>
       <c r="V107" s="5"/>
       <c r="W107" s="5"/>
-      <c r="X107" s="5"/>
-      <c r="Y107" s="5"/>
+      <c r="X107" s="19"/>
+      <c r="Y107" s="38"/>
       <c r="Z107" s="5"/>
       <c r="AA107" s="5"/>
       <c r="AB107" s="5"/>
@@ -5187,8 +5474,8 @@
       <c r="U108" s="5"/>
       <c r="V108" s="5"/>
       <c r="W108" s="5"/>
-      <c r="X108" s="5"/>
-      <c r="Y108" s="5"/>
+      <c r="X108" s="19"/>
+      <c r="Y108" s="38"/>
       <c r="Z108" s="5"/>
       <c r="AA108" s="5"/>
       <c r="AB108" s="5"/>
@@ -5221,8 +5508,8 @@
       <c r="U109" s="5"/>
       <c r="V109" s="5"/>
       <c r="W109" s="5"/>
-      <c r="X109" s="5"/>
-      <c r="Y109" s="5"/>
+      <c r="X109" s="19"/>
+      <c r="Y109" s="38"/>
       <c r="Z109" s="5"/>
       <c r="AA109" s="5"/>
       <c r="AB109" s="5"/>
@@ -5255,8 +5542,8 @@
       <c r="U110" s="5"/>
       <c r="V110" s="5"/>
       <c r="W110" s="5"/>
-      <c r="X110" s="5"/>
-      <c r="Y110" s="5"/>
+      <c r="X110" s="19"/>
+      <c r="Y110" s="38"/>
       <c r="Z110" s="5"/>
       <c r="AA110" s="5"/>
       <c r="AB110" s="5"/>
@@ -5289,8 +5576,8 @@
       <c r="U111" s="5"/>
       <c r="V111" s="5"/>
       <c r="W111" s="5"/>
-      <c r="X111" s="5"/>
-      <c r="Y111" s="5"/>
+      <c r="X111" s="19"/>
+      <c r="Y111" s="38"/>
       <c r="Z111" s="5"/>
       <c r="AA111" s="5"/>
       <c r="AB111" s="5"/>
@@ -5323,8 +5610,8 @@
       <c r="U112" s="5"/>
       <c r="V112" s="5"/>
       <c r="W112" s="5"/>
-      <c r="X112" s="5"/>
-      <c r="Y112" s="5"/>
+      <c r="X112" s="19"/>
+      <c r="Y112" s="38"/>
       <c r="Z112" s="5"/>
       <c r="AA112" s="5"/>
       <c r="AB112" s="5"/>
@@ -5357,8 +5644,8 @@
       <c r="U113" s="5"/>
       <c r="V113" s="5"/>
       <c r="W113" s="5"/>
-      <c r="X113" s="5"/>
-      <c r="Y113" s="5"/>
+      <c r="X113" s="19"/>
+      <c r="Y113" s="38"/>
       <c r="Z113" s="5"/>
       <c r="AA113" s="5"/>
       <c r="AB113" s="5"/>
@@ -5391,8 +5678,8 @@
       <c r="U114" s="5"/>
       <c r="V114" s="5"/>
       <c r="W114" s="5"/>
-      <c r="X114" s="5"/>
-      <c r="Y114" s="5"/>
+      <c r="X114" s="19"/>
+      <c r="Y114" s="38"/>
       <c r="Z114" s="5"/>
       <c r="AA114" s="5"/>
       <c r="AB114" s="5"/>
@@ -5425,8 +5712,8 @@
       <c r="U115" s="5"/>
       <c r="V115" s="5"/>
       <c r="W115" s="5"/>
-      <c r="X115" s="5"/>
-      <c r="Y115" s="5"/>
+      <c r="X115" s="19"/>
+      <c r="Y115" s="38"/>
       <c r="Z115" s="5"/>
       <c r="AA115" s="5"/>
       <c r="AB115" s="5"/>
@@ -5459,8 +5746,8 @@
       <c r="U116" s="5"/>
       <c r="V116" s="5"/>
       <c r="W116" s="5"/>
-      <c r="X116" s="5"/>
-      <c r="Y116" s="5"/>
+      <c r="X116" s="19"/>
+      <c r="Y116" s="38"/>
       <c r="Z116" s="5"/>
       <c r="AA116" s="5"/>
       <c r="AB116" s="5"/>
@@ -5493,8 +5780,8 @@
       <c r="U117" s="5"/>
       <c r="V117" s="5"/>
       <c r="W117" s="5"/>
-      <c r="X117" s="5"/>
-      <c r="Y117" s="5"/>
+      <c r="X117" s="19"/>
+      <c r="Y117" s="38"/>
       <c r="Z117" s="5"/>
       <c r="AA117" s="5"/>
       <c r="AB117" s="5"/>
@@ -5527,8 +5814,8 @@
       <c r="U118" s="5"/>
       <c r="V118" s="5"/>
       <c r="W118" s="5"/>
-      <c r="X118" s="5"/>
-      <c r="Y118" s="5"/>
+      <c r="X118" s="19"/>
+      <c r="Y118" s="38"/>
       <c r="Z118" s="5"/>
       <c r="AA118" s="5"/>
       <c r="AB118" s="5"/>
@@ -5561,8 +5848,8 @@
       <c r="U119" s="5"/>
       <c r="V119" s="5"/>
       <c r="W119" s="5"/>
-      <c r="X119" s="5"/>
-      <c r="Y119" s="5"/>
+      <c r="X119" s="19"/>
+      <c r="Y119" s="38"/>
       <c r="Z119" s="5"/>
       <c r="AA119" s="5"/>
       <c r="AB119" s="5"/>
@@ -5595,8 +5882,8 @@
       <c r="U120" s="5"/>
       <c r="V120" s="5"/>
       <c r="W120" s="5"/>
-      <c r="X120" s="5"/>
-      <c r="Y120" s="5"/>
+      <c r="X120" s="19"/>
+      <c r="Y120" s="38"/>
       <c r="Z120" s="5"/>
       <c r="AA120" s="5"/>
       <c r="AB120" s="5"/>
@@ -5629,8 +5916,8 @@
       <c r="U121" s="5"/>
       <c r="V121" s="5"/>
       <c r="W121" s="5"/>
-      <c r="X121" s="5"/>
-      <c r="Y121" s="5"/>
+      <c r="X121" s="19"/>
+      <c r="Y121" s="38"/>
       <c r="Z121" s="5"/>
       <c r="AA121" s="5"/>
       <c r="AB121" s="5"/>
@@ -5663,8 +5950,8 @@
       <c r="U122" s="5"/>
       <c r="V122" s="5"/>
       <c r="W122" s="5"/>
-      <c r="X122" s="5"/>
-      <c r="Y122" s="5"/>
+      <c r="X122" s="19"/>
+      <c r="Y122" s="38"/>
       <c r="Z122" s="5"/>
       <c r="AA122" s="5"/>
       <c r="AB122" s="5"/>
@@ -5697,8 +5984,8 @@
       <c r="U123" s="5"/>
       <c r="V123" s="5"/>
       <c r="W123" s="5"/>
-      <c r="X123" s="5"/>
-      <c r="Y123" s="5"/>
+      <c r="X123" s="19"/>
+      <c r="Y123" s="38"/>
       <c r="Z123" s="5"/>
       <c r="AA123" s="5"/>
       <c r="AB123" s="5"/>
@@ -5731,8 +6018,8 @@
       <c r="U124" s="5"/>
       <c r="V124" s="5"/>
       <c r="W124" s="5"/>
-      <c r="X124" s="5"/>
-      <c r="Y124" s="5"/>
+      <c r="X124" s="19"/>
+      <c r="Y124" s="38"/>
       <c r="Z124" s="5"/>
       <c r="AA124" s="5"/>
       <c r="AB124" s="5"/>
@@ -5765,8 +6052,8 @@
       <c r="U125" s="5"/>
       <c r="V125" s="5"/>
       <c r="W125" s="5"/>
-      <c r="X125" s="5"/>
-      <c r="Y125" s="5"/>
+      <c r="X125" s="19"/>
+      <c r="Y125" s="38"/>
       <c r="Z125" s="5"/>
       <c r="AA125" s="5"/>
       <c r="AB125" s="5"/>
@@ -5799,8 +6086,8 @@
       <c r="U126" s="5"/>
       <c r="V126" s="5"/>
       <c r="W126" s="5"/>
-      <c r="X126" s="5"/>
-      <c r="Y126" s="5"/>
+      <c r="X126" s="19"/>
+      <c r="Y126" s="38"/>
       <c r="Z126" s="5"/>
       <c r="AA126" s="5"/>
       <c r="AB126" s="5"/>
@@ -5833,8 +6120,8 @@
       <c r="U127" s="5"/>
       <c r="V127" s="5"/>
       <c r="W127" s="5"/>
-      <c r="X127" s="5"/>
-      <c r="Y127" s="5"/>
+      <c r="X127" s="19"/>
+      <c r="Y127" s="38"/>
       <c r="Z127" s="5"/>
       <c r="AA127" s="5"/>
       <c r="AB127" s="5"/>
@@ -5867,8 +6154,8 @@
       <c r="U128" s="5"/>
       <c r="V128" s="5"/>
       <c r="W128" s="5"/>
-      <c r="X128" s="5"/>
-      <c r="Y128" s="5"/>
+      <c r="X128" s="19"/>
+      <c r="Y128" s="38"/>
       <c r="Z128" s="5"/>
       <c r="AA128" s="5"/>
       <c r="AB128" s="5"/>
@@ -5901,8 +6188,8 @@
       <c r="U129" s="5"/>
       <c r="V129" s="5"/>
       <c r="W129" s="5"/>
-      <c r="X129" s="5"/>
-      <c r="Y129" s="5"/>
+      <c r="X129" s="19"/>
+      <c r="Y129" s="38"/>
       <c r="Z129" s="5"/>
       <c r="AA129" s="5"/>
       <c r="AB129" s="5"/>
@@ -5935,8 +6222,8 @@
       <c r="U130" s="5"/>
       <c r="V130" s="5"/>
       <c r="W130" s="5"/>
-      <c r="X130" s="5"/>
-      <c r="Y130" s="5"/>
+      <c r="X130" s="19"/>
+      <c r="Y130" s="38"/>
       <c r="Z130" s="5"/>
       <c r="AA130" s="5"/>
       <c r="AB130" s="5"/>
@@ -5969,8 +6256,8 @@
       <c r="U131" s="5"/>
       <c r="V131" s="5"/>
       <c r="W131" s="5"/>
-      <c r="X131" s="5"/>
-      <c r="Y131" s="5"/>
+      <c r="X131" s="19"/>
+      <c r="Y131" s="38"/>
       <c r="Z131" s="5"/>
       <c r="AA131" s="5"/>
       <c r="AB131" s="5"/>
@@ -6003,8 +6290,8 @@
       <c r="U132" s="5"/>
       <c r="V132" s="5"/>
       <c r="W132" s="5"/>
-      <c r="X132" s="5"/>
-      <c r="Y132" s="5"/>
+      <c r="X132" s="19"/>
+      <c r="Y132" s="38"/>
       <c r="Z132" s="5"/>
       <c r="AA132" s="5"/>
       <c r="AB132" s="5"/>
@@ -6037,8 +6324,8 @@
       <c r="U133" s="5"/>
       <c r="V133" s="5"/>
       <c r="W133" s="5"/>
-      <c r="X133" s="5"/>
-      <c r="Y133" s="5"/>
+      <c r="X133" s="19"/>
+      <c r="Y133" s="38"/>
       <c r="Z133" s="5"/>
       <c r="AA133" s="5"/>
       <c r="AB133" s="5"/>
@@ -6071,8 +6358,8 @@
       <c r="U134" s="5"/>
       <c r="V134" s="5"/>
       <c r="W134" s="5"/>
-      <c r="X134" s="5"/>
-      <c r="Y134" s="5"/>
+      <c r="X134" s="19"/>
+      <c r="Y134" s="38"/>
       <c r="Z134" s="5"/>
       <c r="AA134" s="5"/>
       <c r="AB134" s="5"/>
@@ -6105,8 +6392,8 @@
       <c r="U135" s="5"/>
       <c r="V135" s="5"/>
       <c r="W135" s="5"/>
-      <c r="X135" s="5"/>
-      <c r="Y135" s="5"/>
+      <c r="X135" s="19"/>
+      <c r="Y135" s="38"/>
       <c r="Z135" s="5"/>
       <c r="AA135" s="5"/>
       <c r="AB135" s="5"/>
@@ -6139,8 +6426,8 @@
       <c r="U136" s="5"/>
       <c r="V136" s="5"/>
       <c r="W136" s="5"/>
-      <c r="X136" s="5"/>
-      <c r="Y136" s="5"/>
+      <c r="X136" s="19"/>
+      <c r="Y136" s="38"/>
       <c r="Z136" s="5"/>
       <c r="AA136" s="5"/>
       <c r="AB136" s="5"/>
@@ -6173,8 +6460,8 @@
       <c r="U137" s="5"/>
       <c r="V137" s="5"/>
       <c r="W137" s="5"/>
-      <c r="X137" s="5"/>
-      <c r="Y137" s="5"/>
+      <c r="X137" s="19"/>
+      <c r="Y137" s="38"/>
       <c r="Z137" s="5"/>
       <c r="AA137" s="5"/>
       <c r="AB137" s="5"/>
@@ -6207,8 +6494,8 @@
       <c r="U138" s="5"/>
       <c r="V138" s="5"/>
       <c r="W138" s="5"/>
-      <c r="X138" s="5"/>
-      <c r="Y138" s="5"/>
+      <c r="X138" s="19"/>
+      <c r="Y138" s="38"/>
       <c r="Z138" s="5"/>
       <c r="AA138" s="5"/>
       <c r="AB138" s="5"/>
@@ -6241,8 +6528,8 @@
       <c r="U139" s="5"/>
       <c r="V139" s="5"/>
       <c r="W139" s="5"/>
-      <c r="X139" s="5"/>
-      <c r="Y139" s="5"/>
+      <c r="X139" s="19"/>
+      <c r="Y139" s="38"/>
       <c r="Z139" s="5"/>
       <c r="AA139" s="5"/>
       <c r="AB139" s="5"/>
@@ -6275,8 +6562,8 @@
       <c r="U140" s="5"/>
       <c r="V140" s="5"/>
       <c r="W140" s="5"/>
-      <c r="X140" s="5"/>
-      <c r="Y140" s="5"/>
+      <c r="X140" s="19"/>
+      <c r="Y140" s="38"/>
       <c r="Z140" s="5"/>
       <c r="AA140" s="5"/>
       <c r="AB140" s="5"/>
@@ -6309,8 +6596,8 @@
       <c r="U141" s="5"/>
       <c r="V141" s="5"/>
       <c r="W141" s="5"/>
-      <c r="X141" s="5"/>
-      <c r="Y141" s="5"/>
+      <c r="X141" s="19"/>
+      <c r="Y141" s="38"/>
       <c r="Z141" s="5"/>
       <c r="AA141" s="5"/>
       <c r="AB141" s="5"/>
@@ -6343,8 +6630,8 @@
       <c r="U142" s="5"/>
       <c r="V142" s="5"/>
       <c r="W142" s="5"/>
-      <c r="X142" s="5"/>
-      <c r="Y142" s="5"/>
+      <c r="X142" s="19"/>
+      <c r="Y142" s="38"/>
       <c r="Z142" s="5"/>
       <c r="AA142" s="5"/>
       <c r="AB142" s="5"/>
@@ -6377,8 +6664,8 @@
       <c r="U143" s="5"/>
       <c r="V143" s="5"/>
       <c r="W143" s="5"/>
-      <c r="X143" s="5"/>
-      <c r="Y143" s="5"/>
+      <c r="X143" s="19"/>
+      <c r="Y143" s="38"/>
       <c r="Z143" s="5"/>
       <c r="AA143" s="5"/>
       <c r="AB143" s="5"/>
@@ -6411,8 +6698,8 @@
       <c r="U144" s="5"/>
       <c r="V144" s="5"/>
       <c r="W144" s="5"/>
-      <c r="X144" s="5"/>
-      <c r="Y144" s="5"/>
+      <c r="X144" s="19"/>
+      <c r="Y144" s="38"/>
       <c r="Z144" s="5"/>
       <c r="AA144" s="5"/>
       <c r="AB144" s="5"/>
@@ -6445,8 +6732,8 @@
       <c r="U145" s="5"/>
       <c r="V145" s="5"/>
       <c r="W145" s="5"/>
-      <c r="X145" s="5"/>
-      <c r="Y145" s="5"/>
+      <c r="X145" s="19"/>
+      <c r="Y145" s="38"/>
       <c r="Z145" s="5"/>
       <c r="AA145" s="5"/>
       <c r="AB145" s="5"/>
@@ -6479,8 +6766,8 @@
       <c r="U146" s="5"/>
       <c r="V146" s="5"/>
       <c r="W146" s="5"/>
-      <c r="X146" s="5"/>
-      <c r="Y146" s="5"/>
+      <c r="X146" s="19"/>
+      <c r="Y146" s="38"/>
       <c r="Z146" s="5"/>
       <c r="AA146" s="5"/>
       <c r="AB146" s="5"/>
@@ -6513,8 +6800,8 @@
       <c r="U147" s="5"/>
       <c r="V147" s="5"/>
       <c r="W147" s="5"/>
-      <c r="X147" s="5"/>
-      <c r="Y147" s="5"/>
+      <c r="X147" s="19"/>
+      <c r="Y147" s="38"/>
       <c r="Z147" s="5"/>
       <c r="AA147" s="5"/>
       <c r="AB147" s="5"/>
@@ -6547,8 +6834,8 @@
       <c r="U148" s="5"/>
       <c r="V148" s="5"/>
       <c r="W148" s="5"/>
-      <c r="X148" s="5"/>
-      <c r="Y148" s="5"/>
+      <c r="X148" s="19"/>
+      <c r="Y148" s="38"/>
       <c r="Z148" s="5"/>
       <c r="AA148" s="5"/>
       <c r="AB148" s="5"/>
@@ -6581,8 +6868,8 @@
       <c r="U149" s="5"/>
       <c r="V149" s="5"/>
       <c r="W149" s="5"/>
-      <c r="X149" s="5"/>
-      <c r="Y149" s="5"/>
+      <c r="X149" s="19"/>
+      <c r="Y149" s="38"/>
       <c r="Z149" s="5"/>
       <c r="AA149" s="5"/>
       <c r="AB149" s="5"/>
@@ -6615,8 +6902,8 @@
       <c r="U150" s="5"/>
       <c r="V150" s="5"/>
       <c r="W150" s="5"/>
-      <c r="X150" s="5"/>
-      <c r="Y150" s="5"/>
+      <c r="X150" s="19"/>
+      <c r="Y150" s="38"/>
       <c r="Z150" s="5"/>
       <c r="AA150" s="5"/>
       <c r="AB150" s="5"/>
@@ -6649,8 +6936,8 @@
       <c r="U151" s="5"/>
       <c r="V151" s="5"/>
       <c r="W151" s="5"/>
-      <c r="X151" s="5"/>
-      <c r="Y151" s="5"/>
+      <c r="X151" s="19"/>
+      <c r="Y151" s="38"/>
       <c r="Z151" s="5"/>
       <c r="AA151" s="5"/>
       <c r="AB151" s="5"/>
@@ -6683,8 +6970,8 @@
       <c r="U152" s="5"/>
       <c r="V152" s="5"/>
       <c r="W152" s="5"/>
-      <c r="X152" s="5"/>
-      <c r="Y152" s="5"/>
+      <c r="X152" s="19"/>
+      <c r="Y152" s="38"/>
       <c r="Z152" s="5"/>
       <c r="AA152" s="5"/>
       <c r="AB152" s="5"/>
@@ -6717,8 +7004,8 @@
       <c r="U153" s="5"/>
       <c r="V153" s="5"/>
       <c r="W153" s="5"/>
-      <c r="X153" s="5"/>
-      <c r="Y153" s="5"/>
+      <c r="X153" s="19"/>
+      <c r="Y153" s="38"/>
       <c r="Z153" s="5"/>
       <c r="AA153" s="5"/>
       <c r="AB153" s="5"/>
@@ -6751,8 +7038,8 @@
       <c r="U154" s="5"/>
       <c r="V154" s="5"/>
       <c r="W154" s="5"/>
-      <c r="X154" s="5"/>
-      <c r="Y154" s="5"/>
+      <c r="X154" s="19"/>
+      <c r="Y154" s="38"/>
       <c r="Z154" s="5"/>
       <c r="AA154" s="5"/>
       <c r="AB154" s="5"/>
@@ -6785,8 +7072,8 @@
       <c r="U155" s="5"/>
       <c r="V155" s="5"/>
       <c r="W155" s="5"/>
-      <c r="X155" s="5"/>
-      <c r="Y155" s="5"/>
+      <c r="X155" s="19"/>
+      <c r="Y155" s="38"/>
       <c r="Z155" s="5"/>
       <c r="AA155" s="5"/>
       <c r="AB155" s="5"/>
@@ -6819,8 +7106,8 @@
       <c r="U156" s="5"/>
       <c r="V156" s="5"/>
       <c r="W156" s="5"/>
-      <c r="X156" s="5"/>
-      <c r="Y156" s="5"/>
+      <c r="X156" s="19"/>
+      <c r="Y156" s="38"/>
       <c r="Z156" s="5"/>
       <c r="AA156" s="5"/>
       <c r="AB156" s="5"/>
@@ -6853,8 +7140,8 @@
       <c r="U157" s="5"/>
       <c r="V157" s="5"/>
       <c r="W157" s="5"/>
-      <c r="X157" s="5"/>
-      <c r="Y157" s="5"/>
+      <c r="X157" s="19"/>
+      <c r="Y157" s="38"/>
       <c r="Z157" s="5"/>
       <c r="AA157" s="5"/>
       <c r="AB157" s="5"/>
@@ -6887,8 +7174,8 @@
       <c r="U158" s="5"/>
       <c r="V158" s="5"/>
       <c r="W158" s="5"/>
-      <c r="X158" s="5"/>
-      <c r="Y158" s="5"/>
+      <c r="X158" s="19"/>
+      <c r="Y158" s="38"/>
       <c r="Z158" s="5"/>
       <c r="AA158" s="5"/>
       <c r="AB158" s="5"/>
@@ -6921,8 +7208,8 @@
       <c r="U159" s="5"/>
       <c r="V159" s="5"/>
       <c r="W159" s="5"/>
-      <c r="X159" s="5"/>
-      <c r="Y159" s="5"/>
+      <c r="X159" s="19"/>
+      <c r="Y159" s="38"/>
       <c r="Z159" s="5"/>
       <c r="AA159" s="5"/>
       <c r="AB159" s="5"/>
@@ -6955,8 +7242,8 @@
       <c r="U160" s="5"/>
       <c r="V160" s="5"/>
       <c r="W160" s="5"/>
-      <c r="X160" s="5"/>
-      <c r="Y160" s="5"/>
+      <c r="X160" s="19"/>
+      <c r="Y160" s="38"/>
       <c r="Z160" s="5"/>
       <c r="AA160" s="5"/>
       <c r="AB160" s="5"/>
@@ -6989,8 +7276,8 @@
       <c r="U161" s="5"/>
       <c r="V161" s="5"/>
       <c r="W161" s="5"/>
-      <c r="X161" s="5"/>
-      <c r="Y161" s="5"/>
+      <c r="X161" s="19"/>
+      <c r="Y161" s="38"/>
       <c r="Z161" s="5"/>
       <c r="AA161" s="5"/>
       <c r="AB161" s="5"/>
@@ -7023,8 +7310,8 @@
       <c r="U162" s="5"/>
       <c r="V162" s="5"/>
       <c r="W162" s="5"/>
-      <c r="X162" s="5"/>
-      <c r="Y162" s="5"/>
+      <c r="X162" s="19"/>
+      <c r="Y162" s="38"/>
       <c r="Z162" s="5"/>
       <c r="AA162" s="5"/>
       <c r="AB162" s="5"/>
@@ -7057,8 +7344,8 @@
       <c r="U163" s="5"/>
       <c r="V163" s="5"/>
       <c r="W163" s="5"/>
-      <c r="X163" s="5"/>
-      <c r="Y163" s="5"/>
+      <c r="X163" s="19"/>
+      <c r="Y163" s="38"/>
       <c r="Z163" s="5"/>
       <c r="AA163" s="5"/>
       <c r="AB163" s="5"/>
@@ -7091,8 +7378,8 @@
       <c r="U164" s="5"/>
       <c r="V164" s="5"/>
       <c r="W164" s="5"/>
-      <c r="X164" s="5"/>
-      <c r="Y164" s="5"/>
+      <c r="X164" s="19"/>
+      <c r="Y164" s="38"/>
       <c r="Z164" s="5"/>
       <c r="AA164" s="5"/>
       <c r="AB164" s="5"/>
@@ -7125,8 +7412,8 @@
       <c r="U165" s="5"/>
       <c r="V165" s="5"/>
       <c r="W165" s="5"/>
-      <c r="X165" s="5"/>
-      <c r="Y165" s="5"/>
+      <c r="X165" s="19"/>
+      <c r="Y165" s="38"/>
       <c r="Z165" s="5"/>
       <c r="AA165" s="5"/>
       <c r="AB165" s="5"/>
@@ -7159,8 +7446,8 @@
       <c r="U166" s="5"/>
       <c r="V166" s="5"/>
       <c r="W166" s="5"/>
-      <c r="X166" s="5"/>
-      <c r="Y166" s="5"/>
+      <c r="X166" s="19"/>
+      <c r="Y166" s="38"/>
       <c r="Z166" s="5"/>
       <c r="AA166" s="5"/>
       <c r="AB166" s="5"/>
@@ -7193,8 +7480,8 @@
       <c r="U167" s="5"/>
       <c r="V167" s="5"/>
       <c r="W167" s="5"/>
-      <c r="X167" s="5"/>
-      <c r="Y167" s="5"/>
+      <c r="X167" s="19"/>
+      <c r="Y167" s="38"/>
       <c r="Z167" s="5"/>
       <c r="AA167" s="5"/>
       <c r="AB167" s="5"/>
@@ -7227,8 +7514,8 @@
       <c r="U168" s="5"/>
       <c r="V168" s="5"/>
       <c r="W168" s="5"/>
-      <c r="X168" s="5"/>
-      <c r="Y168" s="5"/>
+      <c r="X168" s="19"/>
+      <c r="Y168" s="38"/>
       <c r="Z168" s="5"/>
       <c r="AA168" s="5"/>
       <c r="AB168" s="5"/>
@@ -7261,8 +7548,8 @@
       <c r="U169" s="5"/>
       <c r="V169" s="5"/>
       <c r="W169" s="5"/>
-      <c r="X169" s="5"/>
-      <c r="Y169" s="5"/>
+      <c r="X169" s="19"/>
+      <c r="Y169" s="38"/>
       <c r="Z169" s="5"/>
       <c r="AA169" s="5"/>
       <c r="AB169" s="5"/>
@@ -7295,8 +7582,8 @@
       <c r="U170" s="5"/>
       <c r="V170" s="5"/>
       <c r="W170" s="5"/>
-      <c r="X170" s="5"/>
-      <c r="Y170" s="5"/>
+      <c r="X170" s="19"/>
+      <c r="Y170" s="38"/>
       <c r="Z170" s="5"/>
       <c r="AA170" s="5"/>
       <c r="AB170" s="5"/>
@@ -7329,8 +7616,8 @@
       <c r="U171" s="5"/>
       <c r="V171" s="5"/>
       <c r="W171" s="5"/>
-      <c r="X171" s="5"/>
-      <c r="Y171" s="5"/>
+      <c r="X171" s="19"/>
+      <c r="Y171" s="38"/>
       <c r="Z171" s="5"/>
       <c r="AA171" s="5"/>
       <c r="AB171" s="5"/>
@@ -7363,8 +7650,8 @@
       <c r="U172" s="5"/>
       <c r="V172" s="5"/>
       <c r="W172" s="5"/>
-      <c r="X172" s="5"/>
-      <c r="Y172" s="5"/>
+      <c r="X172" s="19"/>
+      <c r="Y172" s="38"/>
       <c r="Z172" s="5"/>
       <c r="AA172" s="5"/>
       <c r="AB172" s="5"/>
@@ -7397,8 +7684,8 @@
       <c r="U173" s="5"/>
       <c r="V173" s="5"/>
       <c r="W173" s="5"/>
-      <c r="X173" s="5"/>
-      <c r="Y173" s="5"/>
+      <c r="X173" s="19"/>
+      <c r="Y173" s="38"/>
       <c r="Z173" s="5"/>
       <c r="AA173" s="5"/>
       <c r="AB173" s="5"/>
@@ -7431,8 +7718,8 @@
       <c r="U174" s="5"/>
       <c r="V174" s="5"/>
       <c r="W174" s="5"/>
-      <c r="X174" s="5"/>
-      <c r="Y174" s="5"/>
+      <c r="X174" s="19"/>
+      <c r="Y174" s="38"/>
       <c r="Z174" s="5"/>
       <c r="AA174" s="5"/>
       <c r="AB174" s="5"/>
@@ -7465,8 +7752,8 @@
       <c r="U175" s="5"/>
       <c r="V175" s="5"/>
       <c r="W175" s="5"/>
-      <c r="X175" s="5"/>
-      <c r="Y175" s="5"/>
+      <c r="X175" s="19"/>
+      <c r="Y175" s="38"/>
       <c r="Z175" s="5"/>
       <c r="AA175" s="5"/>
       <c r="AB175" s="5"/>
@@ -7499,8 +7786,8 @@
       <c r="U176" s="5"/>
       <c r="V176" s="5"/>
       <c r="W176" s="5"/>
-      <c r="X176" s="5"/>
-      <c r="Y176" s="5"/>
+      <c r="X176" s="19"/>
+      <c r="Y176" s="38"/>
       <c r="Z176" s="5"/>
       <c r="AA176" s="5"/>
       <c r="AB176" s="5"/>
@@ -7533,8 +7820,8 @@
       <c r="U177" s="5"/>
       <c r="V177" s="5"/>
       <c r="W177" s="5"/>
-      <c r="X177" s="5"/>
-      <c r="Y177" s="5"/>
+      <c r="X177" s="19"/>
+      <c r="Y177" s="38"/>
       <c r="Z177" s="5"/>
       <c r="AA177" s="5"/>
       <c r="AB177" s="5"/>
@@ -7567,8 +7854,8 @@
       <c r="U178" s="5"/>
       <c r="V178" s="5"/>
       <c r="W178" s="5"/>
-      <c r="X178" s="5"/>
-      <c r="Y178" s="5"/>
+      <c r="X178" s="19"/>
+      <c r="Y178" s="38"/>
       <c r="Z178" s="5"/>
       <c r="AA178" s="5"/>
       <c r="AB178" s="5"/>
@@ -7601,8 +7888,8 @@
       <c r="U179" s="5"/>
       <c r="V179" s="5"/>
       <c r="W179" s="5"/>
-      <c r="X179" s="5"/>
-      <c r="Y179" s="5"/>
+      <c r="X179" s="19"/>
+      <c r="Y179" s="38"/>
       <c r="Z179" s="5"/>
       <c r="AA179" s="5"/>
       <c r="AB179" s="5"/>
@@ -7635,8 +7922,8 @@
       <c r="U180" s="5"/>
       <c r="V180" s="5"/>
       <c r="W180" s="5"/>
-      <c r="X180" s="5"/>
-      <c r="Y180" s="5"/>
+      <c r="X180" s="19"/>
+      <c r="Y180" s="38"/>
       <c r="Z180" s="5"/>
       <c r="AA180" s="5"/>
       <c r="AB180" s="5"/>
@@ -7669,8 +7956,8 @@
       <c r="U181" s="5"/>
       <c r="V181" s="5"/>
       <c r="W181" s="5"/>
-      <c r="X181" s="5"/>
-      <c r="Y181" s="5"/>
+      <c r="X181" s="19"/>
+      <c r="Y181" s="38"/>
       <c r="Z181" s="5"/>
       <c r="AA181" s="5"/>
       <c r="AB181" s="5"/>
@@ -7703,8 +7990,8 @@
       <c r="U182" s="5"/>
       <c r="V182" s="5"/>
       <c r="W182" s="5"/>
-      <c r="X182" s="5"/>
-      <c r="Y182" s="5"/>
+      <c r="X182" s="19"/>
+      <c r="Y182" s="38"/>
       <c r="Z182" s="5"/>
       <c r="AA182" s="5"/>
       <c r="AB182" s="5"/>
@@ -7737,8 +8024,8 @@
       <c r="U183" s="5"/>
       <c r="V183" s="5"/>
       <c r="W183" s="5"/>
-      <c r="X183" s="5"/>
-      <c r="Y183" s="5"/>
+      <c r="X183" s="19"/>
+      <c r="Y183" s="38"/>
       <c r="Z183" s="5"/>
       <c r="AA183" s="5"/>
       <c r="AB183" s="5"/>
@@ -7771,8 +8058,8 @@
       <c r="U184" s="5"/>
       <c r="V184" s="5"/>
       <c r="W184" s="5"/>
-      <c r="X184" s="5"/>
-      <c r="Y184" s="5"/>
+      <c r="X184" s="19"/>
+      <c r="Y184" s="38"/>
       <c r="Z184" s="5"/>
       <c r="AA184" s="5"/>
       <c r="AB184" s="5"/>
@@ -7805,8 +8092,8 @@
       <c r="U185" s="5"/>
       <c r="V185" s="5"/>
       <c r="W185" s="5"/>
-      <c r="X185" s="5"/>
-      <c r="Y185" s="5"/>
+      <c r="X185" s="19"/>
+      <c r="Y185" s="38"/>
       <c r="Z185" s="5"/>
       <c r="AA185" s="5"/>
       <c r="AB185" s="5"/>
@@ -7839,8 +8126,8 @@
       <c r="U186" s="5"/>
       <c r="V186" s="5"/>
       <c r="W186" s="5"/>
-      <c r="X186" s="5"/>
-      <c r="Y186" s="5"/>
+      <c r="X186" s="19"/>
+      <c r="Y186" s="38"/>
       <c r="Z186" s="5"/>
       <c r="AA186" s="5"/>
       <c r="AB186" s="5"/>
@@ -7873,8 +8160,8 @@
       <c r="U187" s="5"/>
       <c r="V187" s="5"/>
       <c r="W187" s="5"/>
-      <c r="X187" s="5"/>
-      <c r="Y187" s="5"/>
+      <c r="X187" s="19"/>
+      <c r="Y187" s="38"/>
       <c r="Z187" s="5"/>
       <c r="AA187" s="5"/>
       <c r="AB187" s="5"/>
@@ -7907,8 +8194,8 @@
       <c r="U188" s="5"/>
       <c r="V188" s="5"/>
       <c r="W188" s="5"/>
-      <c r="X188" s="5"/>
-      <c r="Y188" s="5"/>
+      <c r="X188" s="19"/>
+      <c r="Y188" s="38"/>
       <c r="Z188" s="5"/>
       <c r="AA188" s="5"/>
       <c r="AB188" s="5"/>
@@ -7941,8 +8228,8 @@
       <c r="U189" s="5"/>
       <c r="V189" s="5"/>
       <c r="W189" s="5"/>
-      <c r="X189" s="5"/>
-      <c r="Y189" s="5"/>
+      <c r="X189" s="19"/>
+      <c r="Y189" s="38"/>
       <c r="Z189" s="5"/>
       <c r="AA189" s="5"/>
       <c r="AB189" s="5"/>
@@ -7975,8 +8262,8 @@
       <c r="U190" s="5"/>
       <c r="V190" s="5"/>
       <c r="W190" s="5"/>
-      <c r="X190" s="5"/>
-      <c r="Y190" s="5"/>
+      <c r="X190" s="19"/>
+      <c r="Y190" s="38"/>
       <c r="Z190" s="5"/>
       <c r="AA190" s="5"/>
       <c r="AB190" s="5"/>
@@ -8009,8 +8296,8 @@
       <c r="U191" s="5"/>
       <c r="V191" s="5"/>
       <c r="W191" s="5"/>
-      <c r="X191" s="5"/>
-      <c r="Y191" s="5"/>
+      <c r="X191" s="19"/>
+      <c r="Y191" s="38"/>
       <c r="Z191" s="5"/>
       <c r="AA191" s="5"/>
       <c r="AB191" s="5"/>
@@ -8043,8 +8330,8 @@
       <c r="U192" s="5"/>
       <c r="V192" s="5"/>
       <c r="W192" s="5"/>
-      <c r="X192" s="5"/>
-      <c r="Y192" s="5"/>
+      <c r="X192" s="19"/>
+      <c r="Y192" s="38"/>
       <c r="Z192" s="5"/>
       <c r="AA192" s="5"/>
       <c r="AB192" s="5"/>
@@ -8077,8 +8364,8 @@
       <c r="U193" s="5"/>
       <c r="V193" s="5"/>
       <c r="W193" s="5"/>
-      <c r="X193" s="5"/>
-      <c r="Y193" s="5"/>
+      <c r="X193" s="19"/>
+      <c r="Y193" s="38"/>
       <c r="Z193" s="5"/>
       <c r="AA193" s="5"/>
       <c r="AB193" s="5"/>
@@ -8111,8 +8398,8 @@
       <c r="U194" s="5"/>
       <c r="V194" s="5"/>
       <c r="W194" s="5"/>
-      <c r="X194" s="5"/>
-      <c r="Y194" s="5"/>
+      <c r="X194" s="19"/>
+      <c r="Y194" s="38"/>
       <c r="Z194" s="5"/>
       <c r="AA194" s="5"/>
       <c r="AB194" s="5"/>
@@ -8145,8 +8432,8 @@
       <c r="U195" s="5"/>
       <c r="V195" s="5"/>
       <c r="W195" s="5"/>
-      <c r="X195" s="5"/>
-      <c r="Y195" s="5"/>
+      <c r="X195" s="19"/>
+      <c r="Y195" s="38"/>
       <c r="Z195" s="5"/>
       <c r="AA195" s="5"/>
       <c r="AB195" s="5"/>
@@ -8179,8 +8466,8 @@
       <c r="U196" s="5"/>
       <c r="V196" s="5"/>
       <c r="W196" s="5"/>
-      <c r="X196" s="5"/>
-      <c r="Y196" s="5"/>
+      <c r="X196" s="19"/>
+      <c r="Y196" s="38"/>
       <c r="Z196" s="5"/>
       <c r="AA196" s="5"/>
       <c r="AB196" s="5"/>
@@ -8213,8 +8500,8 @@
       <c r="U197" s="5"/>
       <c r="V197" s="5"/>
       <c r="W197" s="5"/>
-      <c r="X197" s="5"/>
-      <c r="Y197" s="5"/>
+      <c r="X197" s="19"/>
+      <c r="Y197" s="38"/>
       <c r="Z197" s="5"/>
       <c r="AA197" s="5"/>
       <c r="AB197" s="5"/>
@@ -8247,8 +8534,8 @@
       <c r="U198" s="5"/>
       <c r="V198" s="5"/>
       <c r="W198" s="5"/>
-      <c r="X198" s="5"/>
-      <c r="Y198" s="5"/>
+      <c r="X198" s="19"/>
+      <c r="Y198" s="38"/>
       <c r="Z198" s="5"/>
       <c r="AA198" s="5"/>
       <c r="AB198" s="5"/>
@@ -8281,8 +8568,8 @@
       <c r="U199" s="5"/>
       <c r="V199" s="5"/>
       <c r="W199" s="5"/>
-      <c r="X199" s="5"/>
-      <c r="Y199" s="5"/>
+      <c r="X199" s="19"/>
+      <c r="Y199" s="38"/>
       <c r="Z199" s="5"/>
       <c r="AA199" s="5"/>
       <c r="AB199" s="5"/>
@@ -8315,8 +8602,8 @@
       <c r="U200" s="5"/>
       <c r="V200" s="5"/>
       <c r="W200" s="5"/>
-      <c r="X200" s="5"/>
-      <c r="Y200" s="5"/>
+      <c r="X200" s="19"/>
+      <c r="Y200" s="38"/>
       <c r="Z200" s="5"/>
       <c r="AA200" s="5"/>
       <c r="AB200" s="5"/>
@@ -8349,8 +8636,8 @@
       <c r="U201" s="5"/>
       <c r="V201" s="5"/>
       <c r="W201" s="5"/>
-      <c r="X201" s="5"/>
-      <c r="Y201" s="5"/>
+      <c r="X201" s="19"/>
+      <c r="Y201" s="38"/>
       <c r="Z201" s="5"/>
       <c r="AA201" s="5"/>
       <c r="AB201" s="5"/>
@@ -8383,8 +8670,8 @@
       <c r="U202" s="5"/>
       <c r="V202" s="5"/>
       <c r="W202" s="5"/>
-      <c r="X202" s="5"/>
-      <c r="Y202" s="5"/>
+      <c r="X202" s="19"/>
+      <c r="Y202" s="38"/>
       <c r="Z202" s="5"/>
       <c r="AA202" s="5"/>
       <c r="AB202" s="5"/>
@@ -8417,8 +8704,8 @@
       <c r="U203" s="5"/>
       <c r="V203" s="5"/>
       <c r="W203" s="5"/>
-      <c r="X203" s="5"/>
-      <c r="Y203" s="5"/>
+      <c r="X203" s="19"/>
+      <c r="Y203" s="38"/>
       <c r="Z203" s="5"/>
       <c r="AA203" s="5"/>
       <c r="AB203" s="5"/>
@@ -8451,8 +8738,8 @@
       <c r="U204" s="5"/>
       <c r="V204" s="5"/>
       <c r="W204" s="5"/>
-      <c r="X204" s="5"/>
-      <c r="Y204" s="5"/>
+      <c r="X204" s="19"/>
+      <c r="Y204" s="38"/>
       <c r="Z204" s="5"/>
       <c r="AA204" s="5"/>
       <c r="AB204" s="5"/>
@@ -8485,8 +8772,8 @@
       <c r="U205" s="5"/>
       <c r="V205" s="5"/>
       <c r="W205" s="5"/>
-      <c r="X205" s="5"/>
-      <c r="Y205" s="5"/>
+      <c r="X205" s="19"/>
+      <c r="Y205" s="38"/>
       <c r="Z205" s="5"/>
       <c r="AA205" s="5"/>
       <c r="AB205" s="5"/>
@@ -8519,8 +8806,8 @@
       <c r="U206" s="5"/>
       <c r="V206" s="5"/>
       <c r="W206" s="5"/>
-      <c r="X206" s="5"/>
-      <c r="Y206" s="5"/>
+      <c r="X206" s="19"/>
+      <c r="Y206" s="38"/>
       <c r="Z206" s="5"/>
       <c r="AA206" s="5"/>
       <c r="AB206" s="5"/>
@@ -8553,8 +8840,8 @@
       <c r="U207" s="5"/>
       <c r="V207" s="5"/>
       <c r="W207" s="5"/>
-      <c r="X207" s="5"/>
-      <c r="Y207" s="5"/>
+      <c r="X207" s="19"/>
+      <c r="Y207" s="38"/>
       <c r="Z207" s="5"/>
       <c r="AA207" s="5"/>
       <c r="AB207" s="5"/>
@@ -8587,8 +8874,8 @@
       <c r="U208" s="5"/>
       <c r="V208" s="5"/>
       <c r="W208" s="5"/>
-      <c r="X208" s="5"/>
-      <c r="Y208" s="5"/>
+      <c r="X208" s="19"/>
+      <c r="Y208" s="38"/>
       <c r="Z208" s="5"/>
       <c r="AA208" s="5"/>
       <c r="AB208" s="5"/>
@@ -8621,8 +8908,8 @@
       <c r="U209" s="5"/>
       <c r="V209" s="5"/>
       <c r="W209" s="5"/>
-      <c r="X209" s="5"/>
-      <c r="Y209" s="5"/>
+      <c r="X209" s="19"/>
+      <c r="Y209" s="38"/>
       <c r="Z209" s="5"/>
       <c r="AA209" s="5"/>
       <c r="AB209" s="5"/>
@@ -8655,8 +8942,8 @@
       <c r="U210" s="5"/>
       <c r="V210" s="5"/>
       <c r="W210" s="5"/>
-      <c r="X210" s="5"/>
-      <c r="Y210" s="5"/>
+      <c r="X210" s="19"/>
+      <c r="Y210" s="38"/>
       <c r="Z210" s="5"/>
       <c r="AA210" s="5"/>
       <c r="AB210" s="5"/>
@@ -8689,8 +8976,8 @@
       <c r="U211" s="5"/>
       <c r="V211" s="5"/>
       <c r="W211" s="5"/>
-      <c r="X211" s="5"/>
-      <c r="Y211" s="5"/>
+      <c r="X211" s="19"/>
+      <c r="Y211" s="38"/>
       <c r="Z211" s="5"/>
       <c r="AA211" s="5"/>
       <c r="AB211" s="5"/>
@@ -8723,8 +9010,8 @@
       <c r="U212" s="5"/>
       <c r="V212" s="5"/>
       <c r="W212" s="5"/>
-      <c r="X212" s="5"/>
-      <c r="Y212" s="5"/>
+      <c r="X212" s="19"/>
+      <c r="Y212" s="38"/>
       <c r="Z212" s="5"/>
       <c r="AA212" s="5"/>
       <c r="AB212" s="5"/>
@@ -8757,8 +9044,8 @@
       <c r="U213" s="5"/>
       <c r="V213" s="5"/>
       <c r="W213" s="5"/>
-      <c r="X213" s="5"/>
-      <c r="Y213" s="5"/>
+      <c r="X213" s="19"/>
+      <c r="Y213" s="38"/>
       <c r="Z213" s="5"/>
       <c r="AA213" s="5"/>
       <c r="AB213" s="5"/>
@@ -8791,8 +9078,8 @@
       <c r="U214" s="5"/>
       <c r="V214" s="5"/>
       <c r="W214" s="5"/>
-      <c r="X214" s="5"/>
-      <c r="Y214" s="5"/>
+      <c r="X214" s="19"/>
+      <c r="Y214" s="38"/>
       <c r="Z214" s="5"/>
       <c r="AA214" s="5"/>
       <c r="AB214" s="5"/>
@@ -8825,8 +9112,8 @@
       <c r="U215" s="5"/>
       <c r="V215" s="5"/>
       <c r="W215" s="5"/>
-      <c r="X215" s="5"/>
-      <c r="Y215" s="5"/>
+      <c r="X215" s="19"/>
+      <c r="Y215" s="38"/>
       <c r="Z215" s="5"/>
       <c r="AA215" s="5"/>
       <c r="AB215" s="5"/>
@@ -8859,8 +9146,8 @@
       <c r="U216" s="5"/>
       <c r="V216" s="5"/>
       <c r="W216" s="5"/>
-      <c r="X216" s="5"/>
-      <c r="Y216" s="5"/>
+      <c r="X216" s="19"/>
+      <c r="Y216" s="38"/>
       <c r="Z216" s="5"/>
       <c r="AA216" s="5"/>
       <c r="AB216" s="5"/>
@@ -8893,8 +9180,8 @@
       <c r="U217" s="5"/>
       <c r="V217" s="5"/>
       <c r="W217" s="5"/>
-      <c r="X217" s="5"/>
-      <c r="Y217" s="5"/>
+      <c r="X217" s="19"/>
+      <c r="Y217" s="38"/>
       <c r="Z217" s="5"/>
       <c r="AA217" s="5"/>
       <c r="AB217" s="5"/>
@@ -8927,8 +9214,8 @@
       <c r="U218" s="5"/>
       <c r="V218" s="5"/>
       <c r="W218" s="5"/>
-      <c r="X218" s="5"/>
-      <c r="Y218" s="5"/>
+      <c r="X218" s="19"/>
+      <c r="Y218" s="38"/>
       <c r="Z218" s="5"/>
       <c r="AA218" s="5"/>
       <c r="AB218" s="5"/>
@@ -8961,8 +9248,8 @@
       <c r="U219" s="5"/>
       <c r="V219" s="5"/>
       <c r="W219" s="5"/>
-      <c r="X219" s="5"/>
-      <c r="Y219" s="5"/>
+      <c r="X219" s="19"/>
+      <c r="Y219" s="38"/>
       <c r="Z219" s="5"/>
       <c r="AA219" s="5"/>
       <c r="AB219" s="5"/>
@@ -8995,8 +9282,8 @@
       <c r="U220" s="5"/>
       <c r="V220" s="5"/>
       <c r="W220" s="5"/>
-      <c r="X220" s="5"/>
-      <c r="Y220" s="5"/>
+      <c r="X220" s="19"/>
+      <c r="Y220" s="38"/>
       <c r="Z220" s="5"/>
       <c r="AA220" s="5"/>
       <c r="AB220" s="5"/>
@@ -9029,8 +9316,8 @@
       <c r="U221" s="5"/>
       <c r="V221" s="5"/>
       <c r="W221" s="5"/>
-      <c r="X221" s="5"/>
-      <c r="Y221" s="5"/>
+      <c r="X221" s="19"/>
+      <c r="Y221" s="38"/>
       <c r="Z221" s="5"/>
       <c r="AA221" s="5"/>
       <c r="AB221" s="5"/>
@@ -9063,8 +9350,8 @@
       <c r="U222" s="5"/>
       <c r="V222" s="5"/>
       <c r="W222" s="5"/>
-      <c r="X222" s="5"/>
-      <c r="Y222" s="5"/>
+      <c r="X222" s="19"/>
+      <c r="Y222" s="38"/>
       <c r="Z222" s="5"/>
       <c r="AA222" s="5"/>
       <c r="AB222" s="5"/>
@@ -9097,8 +9384,8 @@
       <c r="U223" s="5"/>
       <c r="V223" s="5"/>
       <c r="W223" s="5"/>
-      <c r="X223" s="5"/>
-      <c r="Y223" s="5"/>
+      <c r="X223" s="19"/>
+      <c r="Y223" s="38"/>
       <c r="Z223" s="5"/>
       <c r="AA223" s="5"/>
       <c r="AB223" s="5"/>
@@ -9131,8 +9418,8 @@
       <c r="U224" s="5"/>
       <c r="V224" s="5"/>
       <c r="W224" s="5"/>
-      <c r="X224" s="5"/>
-      <c r="Y224" s="5"/>
+      <c r="X224" s="19"/>
+      <c r="Y224" s="38"/>
       <c r="Z224" s="5"/>
       <c r="AA224" s="5"/>
       <c r="AB224" s="5"/>
@@ -9165,8 +9452,8 @@
       <c r="U225" s="5"/>
       <c r="V225" s="5"/>
       <c r="W225" s="5"/>
-      <c r="X225" s="5"/>
-      <c r="Y225" s="5"/>
+      <c r="X225" s="19"/>
+      <c r="Y225" s="38"/>
       <c r="Z225" s="5"/>
       <c r="AA225" s="5"/>
       <c r="AB225" s="5"/>
@@ -9199,8 +9486,8 @@
       <c r="U226" s="5"/>
       <c r="V226" s="5"/>
       <c r="W226" s="5"/>
-      <c r="X226" s="5"/>
-      <c r="Y226" s="5"/>
+      <c r="X226" s="19"/>
+      <c r="Y226" s="38"/>
       <c r="Z226" s="5"/>
       <c r="AA226" s="5"/>
       <c r="AB226" s="5"/>
@@ -9233,8 +9520,8 @@
       <c r="U227" s="5"/>
       <c r="V227" s="5"/>
       <c r="W227" s="5"/>
-      <c r="X227" s="5"/>
-      <c r="Y227" s="5"/>
+      <c r="X227" s="19"/>
+      <c r="Y227" s="38"/>
       <c r="Z227" s="5"/>
       <c r="AA227" s="5"/>
       <c r="AB227" s="5"/>
@@ -9267,8 +9554,8 @@
       <c r="U228" s="5"/>
       <c r="V228" s="5"/>
       <c r="W228" s="5"/>
-      <c r="X228" s="5"/>
-      <c r="Y228" s="5"/>
+      <c r="X228" s="19"/>
+      <c r="Y228" s="38"/>
       <c r="Z228" s="5"/>
       <c r="AA228" s="5"/>
       <c r="AB228" s="5"/>
@@ -9301,8 +9588,8 @@
       <c r="U229" s="5"/>
       <c r="V229" s="5"/>
       <c r="W229" s="5"/>
-      <c r="X229" s="5"/>
-      <c r="Y229" s="5"/>
+      <c r="X229" s="19"/>
+      <c r="Y229" s="38"/>
       <c r="Z229" s="5"/>
       <c r="AA229" s="5"/>
       <c r="AB229" s="5"/>
@@ -9335,8 +9622,8 @@
       <c r="U230" s="5"/>
       <c r="V230" s="5"/>
       <c r="W230" s="5"/>
-      <c r="X230" s="5"/>
-      <c r="Y230" s="5"/>
+      <c r="X230" s="19"/>
+      <c r="Y230" s="38"/>
       <c r="Z230" s="5"/>
       <c r="AA230" s="5"/>
       <c r="AB230" s="5"/>
@@ -9369,8 +9656,8 @@
       <c r="U231" s="5"/>
       <c r="V231" s="5"/>
       <c r="W231" s="5"/>
-      <c r="X231" s="5"/>
-      <c r="Y231" s="5"/>
+      <c r="X231" s="19"/>
+      <c r="Y231" s="38"/>
       <c r="Z231" s="5"/>
       <c r="AA231" s="5"/>
       <c r="AB231" s="5"/>
@@ -9403,8 +9690,8 @@
       <c r="U232" s="5"/>
       <c r="V232" s="5"/>
       <c r="W232" s="5"/>
-      <c r="X232" s="5"/>
-      <c r="Y232" s="5"/>
+      <c r="X232" s="19"/>
+      <c r="Y232" s="38"/>
       <c r="Z232" s="5"/>
       <c r="AA232" s="5"/>
       <c r="AB232" s="5"/>
@@ -9437,8 +9724,8 @@
       <c r="U233" s="5"/>
       <c r="V233" s="5"/>
       <c r="W233" s="5"/>
-      <c r="X233" s="5"/>
-      <c r="Y233" s="5"/>
+      <c r="X233" s="19"/>
+      <c r="Y233" s="38"/>
       <c r="Z233" s="5"/>
       <c r="AA233" s="5"/>
       <c r="AB233" s="5"/>
@@ -9471,8 +9758,8 @@
       <c r="U234" s="5"/>
       <c r="V234" s="5"/>
       <c r="W234" s="5"/>
-      <c r="X234" s="5"/>
-      <c r="Y234" s="5"/>
+      <c r="X234" s="19"/>
+      <c r="Y234" s="38"/>
       <c r="Z234" s="5"/>
       <c r="AA234" s="5"/>
       <c r="AB234" s="5"/>
@@ -9505,8 +9792,8 @@
       <c r="U235" s="5"/>
       <c r="V235" s="5"/>
       <c r="W235" s="5"/>
-      <c r="X235" s="5"/>
-      <c r="Y235" s="5"/>
+      <c r="X235" s="19"/>
+      <c r="Y235" s="38"/>
       <c r="Z235" s="5"/>
       <c r="AA235" s="5"/>
       <c r="AB235" s="5"/>
@@ -9539,8 +9826,8 @@
       <c r="U236" s="5"/>
       <c r="V236" s="5"/>
       <c r="W236" s="5"/>
-      <c r="X236" s="5"/>
-      <c r="Y236" s="5"/>
+      <c r="X236" s="19"/>
+      <c r="Y236" s="38"/>
       <c r="Z236" s="5"/>
       <c r="AA236" s="5"/>
       <c r="AB236" s="5"/>
@@ -9573,8 +9860,8 @@
       <c r="U237" s="5"/>
       <c r="V237" s="5"/>
       <c r="W237" s="5"/>
-      <c r="X237" s="5"/>
-      <c r="Y237" s="5"/>
+      <c r="X237" s="19"/>
+      <c r="Y237" s="38"/>
       <c r="Z237" s="5"/>
       <c r="AA237" s="5"/>
       <c r="AB237" s="5"/>
@@ -9607,8 +9894,8 @@
       <c r="U238" s="5"/>
       <c r="V238" s="5"/>
       <c r="W238" s="5"/>
-      <c r="X238" s="5"/>
-      <c r="Y238" s="5"/>
+      <c r="X238" s="19"/>
+      <c r="Y238" s="38"/>
       <c r="Z238" s="5"/>
       <c r="AA238" s="5"/>
       <c r="AB238" s="5"/>
@@ -9641,8 +9928,8 @@
       <c r="U239" s="5"/>
       <c r="V239" s="5"/>
       <c r="W239" s="5"/>
-      <c r="X239" s="5"/>
-      <c r="Y239" s="5"/>
+      <c r="X239" s="19"/>
+      <c r="Y239" s="38"/>
       <c r="Z239" s="5"/>
       <c r="AA239" s="5"/>
       <c r="AB239" s="5"/>
@@ -9675,8 +9962,8 @@
       <c r="U240" s="5"/>
       <c r="V240" s="5"/>
       <c r="W240" s="5"/>
-      <c r="X240" s="5"/>
-      <c r="Y240" s="5"/>
+      <c r="X240" s="19"/>
+      <c r="Y240" s="38"/>
       <c r="Z240" s="5"/>
       <c r="AA240" s="5"/>
       <c r="AB240" s="5"/>
@@ -9709,8 +9996,8 @@
       <c r="U241" s="5"/>
       <c r="V241" s="5"/>
       <c r="W241" s="5"/>
-      <c r="X241" s="5"/>
-      <c r="Y241" s="5"/>
+      <c r="X241" s="19"/>
+      <c r="Y241" s="38"/>
       <c r="Z241" s="5"/>
       <c r="AA241" s="5"/>
       <c r="AB241" s="5"/>
@@ -9743,8 +10030,8 @@
       <c r="U242" s="5"/>
       <c r="V242" s="5"/>
       <c r="W242" s="5"/>
-      <c r="X242" s="5"/>
-      <c r="Y242" s="5"/>
+      <c r="X242" s="19"/>
+      <c r="Y242" s="38"/>
       <c r="Z242" s="5"/>
       <c r="AA242" s="5"/>
       <c r="AB242" s="5"/>
@@ -9777,8 +10064,8 @@
       <c r="U243" s="5"/>
       <c r="V243" s="5"/>
       <c r="W243" s="5"/>
-      <c r="X243" s="5"/>
-      <c r="Y243" s="5"/>
+      <c r="X243" s="19"/>
+      <c r="Y243" s="38"/>
       <c r="Z243" s="5"/>
       <c r="AA243" s="5"/>
       <c r="AB243" s="5"/>
@@ -9811,8 +10098,8 @@
       <c r="U244" s="5"/>
       <c r="V244" s="5"/>
       <c r="W244" s="5"/>
-      <c r="X244" s="5"/>
-      <c r="Y244" s="5"/>
+      <c r="X244" s="19"/>
+      <c r="Y244" s="38"/>
       <c r="Z244" s="5"/>
       <c r="AA244" s="5"/>
       <c r="AB244" s="5"/>
@@ -9845,8 +10132,8 @@
       <c r="U245" s="5"/>
       <c r="V245" s="5"/>
       <c r="W245" s="5"/>
-      <c r="X245" s="5"/>
-      <c r="Y245" s="5"/>
+      <c r="X245" s="19"/>
+      <c r="Y245" s="38"/>
       <c r="Z245" s="5"/>
       <c r="AA245" s="5"/>
       <c r="AB245" s="5"/>
@@ -9879,8 +10166,8 @@
       <c r="U246" s="5"/>
       <c r="V246" s="5"/>
       <c r="W246" s="5"/>
-      <c r="X246" s="5"/>
-      <c r="Y246" s="5"/>
+      <c r="X246" s="19"/>
+      <c r="Y246" s="38"/>
       <c r="Z246" s="5"/>
       <c r="AA246" s="5"/>
       <c r="AB246" s="5"/>
@@ -9913,8 +10200,8 @@
       <c r="U247" s="5"/>
       <c r="V247" s="5"/>
       <c r="W247" s="5"/>
-      <c r="X247" s="5"/>
-      <c r="Y247" s="5"/>
+      <c r="X247" s="19"/>
+      <c r="Y247" s="38"/>
       <c r="Z247" s="5"/>
       <c r="AA247" s="5"/>
       <c r="AB247" s="5"/>
@@ -9947,8 +10234,8 @@
       <c r="U248" s="5"/>
       <c r="V248" s="5"/>
       <c r="W248" s="5"/>
-      <c r="X248" s="5"/>
-      <c r="Y248" s="5"/>
+      <c r="X248" s="19"/>
+      <c r="Y248" s="38"/>
       <c r="Z248" s="5"/>
       <c r="AA248" s="5"/>
       <c r="AB248" s="5"/>
@@ -9981,8 +10268,8 @@
       <c r="U249" s="5"/>
       <c r="V249" s="5"/>
       <c r="W249" s="5"/>
-      <c r="X249" s="5"/>
-      <c r="Y249" s="5"/>
+      <c r="X249" s="19"/>
+      <c r="Y249" s="38"/>
       <c r="Z249" s="5"/>
       <c r="AA249" s="5"/>
       <c r="AB249" s="5"/>
@@ -10015,8 +10302,8 @@
       <c r="U250" s="5"/>
       <c r="V250" s="5"/>
       <c r="W250" s="5"/>
-      <c r="X250" s="5"/>
-      <c r="Y250" s="5"/>
+      <c r="X250" s="19"/>
+      <c r="Y250" s="38"/>
       <c r="Z250" s="5"/>
       <c r="AA250" s="5"/>
       <c r="AB250" s="5"/>
@@ -10049,8 +10336,8 @@
       <c r="U251" s="5"/>
       <c r="V251" s="5"/>
       <c r="W251" s="5"/>
-      <c r="X251" s="5"/>
-      <c r="Y251" s="5"/>
+      <c r="X251" s="19"/>
+      <c r="Y251" s="38"/>
       <c r="Z251" s="5"/>
       <c r="AA251" s="5"/>
       <c r="AB251" s="5"/>
@@ -10083,8 +10370,8 @@
       <c r="U252" s="5"/>
       <c r="V252" s="5"/>
       <c r="W252" s="5"/>
-      <c r="X252" s="5"/>
-      <c r="Y252" s="5"/>
+      <c r="X252" s="19"/>
+      <c r="Y252" s="38"/>
       <c r="Z252" s="5"/>
       <c r="AA252" s="5"/>
       <c r="AB252" s="5"/>
@@ -10117,8 +10404,8 @@
       <c r="U253" s="5"/>
       <c r="V253" s="5"/>
       <c r="W253" s="5"/>
-      <c r="X253" s="5"/>
-      <c r="Y253" s="5"/>
+      <c r="X253" s="19"/>
+      <c r="Y253" s="38"/>
       <c r="Z253" s="5"/>
       <c r="AA253" s="5"/>
       <c r="AB253" s="5"/>
@@ -10151,8 +10438,8 @@
       <c r="U254" s="5"/>
       <c r="V254" s="5"/>
       <c r="W254" s="5"/>
-      <c r="X254" s="5"/>
-      <c r="Y254" s="5"/>
+      <c r="X254" s="19"/>
+      <c r="Y254" s="38"/>
       <c r="Z254" s="5"/>
       <c r="AA254" s="5"/>
       <c r="AB254" s="5"/>
@@ -10185,8 +10472,8 @@
       <c r="U255" s="5"/>
       <c r="V255" s="5"/>
       <c r="W255" s="5"/>
-      <c r="X255" s="5"/>
-      <c r="Y255" s="5"/>
+      <c r="X255" s="19"/>
+      <c r="Y255" s="38"/>
       <c r="Z255" s="5"/>
       <c r="AA255" s="5"/>
       <c r="AB255" s="5"/>
@@ -10219,8 +10506,8 @@
       <c r="U256" s="5"/>
       <c r="V256" s="5"/>
       <c r="W256" s="5"/>
-      <c r="X256" s="5"/>
-      <c r="Y256" s="5"/>
+      <c r="X256" s="19"/>
+      <c r="Y256" s="38"/>
       <c r="Z256" s="5"/>
       <c r="AA256" s="5"/>
       <c r="AB256" s="5"/>
@@ -10253,8 +10540,8 @@
       <c r="U257" s="5"/>
       <c r="V257" s="5"/>
       <c r="W257" s="5"/>
-      <c r="X257" s="5"/>
-      <c r="Y257" s="5"/>
+      <c r="X257" s="19"/>
+      <c r="Y257" s="38"/>
       <c r="Z257" s="5"/>
       <c r="AA257" s="5"/>
       <c r="AB257" s="5"/>
@@ -10287,8 +10574,8 @@
       <c r="U258" s="5"/>
       <c r="V258" s="5"/>
       <c r="W258" s="5"/>
-      <c r="X258" s="5"/>
-      <c r="Y258" s="5"/>
+      <c r="X258" s="19"/>
+      <c r="Y258" s="38"/>
       <c r="Z258" s="5"/>
       <c r="AA258" s="5"/>
       <c r="AB258" s="5"/>
@@ -10321,8 +10608,8 @@
       <c r="U259" s="5"/>
       <c r="V259" s="5"/>
       <c r="W259" s="5"/>
-      <c r="X259" s="5"/>
-      <c r="Y259" s="5"/>
+      <c r="X259" s="19"/>
+      <c r="Y259" s="38"/>
       <c r="Z259" s="5"/>
       <c r="AA259" s="5"/>
       <c r="AB259" s="5"/>
@@ -10355,8 +10642,8 @@
       <c r="U260" s="5"/>
       <c r="V260" s="5"/>
       <c r="W260" s="5"/>
-      <c r="X260" s="5"/>
-      <c r="Y260" s="5"/>
+      <c r="X260" s="19"/>
+      <c r="Y260" s="38"/>
       <c r="Z260" s="5"/>
       <c r="AA260" s="5"/>
       <c r="AB260" s="5"/>
@@ -10389,8 +10676,8 @@
       <c r="U261" s="5"/>
       <c r="V261" s="5"/>
       <c r="W261" s="5"/>
-      <c r="X261" s="5"/>
-      <c r="Y261" s="5"/>
+      <c r="X261" s="19"/>
+      <c r="Y261" s="38"/>
       <c r="Z261" s="5"/>
       <c r="AA261" s="5"/>
       <c r="AB261" s="5"/>
@@ -10423,8 +10710,8 @@
       <c r="U262" s="5"/>
       <c r="V262" s="5"/>
       <c r="W262" s="5"/>
-      <c r="X262" s="5"/>
-      <c r="Y262" s="5"/>
+      <c r="X262" s="19"/>
+      <c r="Y262" s="38"/>
       <c r="Z262" s="5"/>
       <c r="AA262" s="5"/>
       <c r="AB262" s="5"/>
@@ -10457,8 +10744,8 @@
       <c r="U263" s="5"/>
       <c r="V263" s="5"/>
       <c r="W263" s="5"/>
-      <c r="X263" s="5"/>
-      <c r="Y263" s="5"/>
+      <c r="X263" s="19"/>
+      <c r="Y263" s="38"/>
       <c r="Z263" s="5"/>
       <c r="AA263" s="5"/>
       <c r="AB263" s="5"/>
@@ -10491,8 +10778,8 @@
       <c r="U264" s="5"/>
       <c r="V264" s="5"/>
       <c r="W264" s="5"/>
-      <c r="X264" s="5"/>
-      <c r="Y264" s="5"/>
+      <c r="X264" s="19"/>
+      <c r="Y264" s="38"/>
       <c r="Z264" s="5"/>
       <c r="AA264" s="5"/>
       <c r="AB264" s="5"/>
@@ -10525,8 +10812,8 @@
       <c r="U265" s="5"/>
       <c r="V265" s="5"/>
       <c r="W265" s="5"/>
-      <c r="X265" s="5"/>
-      <c r="Y265" s="5"/>
+      <c r="X265" s="19"/>
+      <c r="Y265" s="38"/>
       <c r="Z265" s="5"/>
       <c r="AA265" s="5"/>
       <c r="AB265" s="5"/>
@@ -10559,8 +10846,8 @@
       <c r="U266" s="5"/>
       <c r="V266" s="5"/>
       <c r="W266" s="5"/>
-      <c r="X266" s="5"/>
-      <c r="Y266" s="5"/>
+      <c r="X266" s="19"/>
+      <c r="Y266" s="38"/>
       <c r="Z266" s="5"/>
       <c r="AA266" s="5"/>
       <c r="AB266" s="5"/>
@@ -10593,8 +10880,8 @@
       <c r="U267" s="5"/>
       <c r="V267" s="5"/>
       <c r="W267" s="5"/>
-      <c r="X267" s="5"/>
-      <c r="Y267" s="5"/>
+      <c r="X267" s="19"/>
+      <c r="Y267" s="38"/>
       <c r="Z267" s="5"/>
       <c r="AA267" s="5"/>
       <c r="AB267" s="5"/>
@@ -10627,8 +10914,8 @@
       <c r="U268" s="5"/>
       <c r="V268" s="5"/>
       <c r="W268" s="5"/>
-      <c r="X268" s="5"/>
-      <c r="Y268" s="5"/>
+      <c r="X268" s="19"/>
+      <c r="Y268" s="38"/>
       <c r="Z268" s="5"/>
       <c r="AA268" s="5"/>
       <c r="AB268" s="5"/>
@@ -10661,8 +10948,8 @@
       <c r="U269" s="5"/>
       <c r="V269" s="5"/>
       <c r="W269" s="5"/>
-      <c r="X269" s="5"/>
-      <c r="Y269" s="5"/>
+      <c r="X269" s="19"/>
+      <c r="Y269" s="38"/>
       <c r="Z269" s="5"/>
       <c r="AA269" s="5"/>
       <c r="AB269" s="5"/>
@@ -10695,8 +10982,8 @@
       <c r="U270" s="5"/>
       <c r="V270" s="5"/>
       <c r="W270" s="5"/>
-      <c r="X270" s="5"/>
-      <c r="Y270" s="5"/>
+      <c r="X270" s="19"/>
+      <c r="Y270" s="38"/>
       <c r="Z270" s="5"/>
       <c r="AA270" s="5"/>
       <c r="AB270" s="5"/>
@@ -10729,8 +11016,8 @@
       <c r="U271" s="5"/>
       <c r="V271" s="5"/>
       <c r="W271" s="5"/>
-      <c r="X271" s="5"/>
-      <c r="Y271" s="5"/>
+      <c r="X271" s="19"/>
+      <c r="Y271" s="38"/>
       <c r="Z271" s="5"/>
       <c r="AA271" s="5"/>
       <c r="AB271" s="5"/>
@@ -10763,8 +11050,8 @@
       <c r="U272" s="5"/>
       <c r="V272" s="5"/>
       <c r="W272" s="5"/>
-      <c r="X272" s="5"/>
-      <c r="Y272" s="5"/>
+      <c r="X272" s="19"/>
+      <c r="Y272" s="38"/>
       <c r="Z272" s="5"/>
       <c r="AA272" s="5"/>
       <c r="AB272" s="5"/>
@@ -10797,8 +11084,8 @@
       <c r="U273" s="5"/>
       <c r="V273" s="5"/>
       <c r="W273" s="5"/>
-      <c r="X273" s="5"/>
-      <c r="Y273" s="5"/>
+      <c r="X273" s="19"/>
+      <c r="Y273" s="38"/>
       <c r="Z273" s="5"/>
       <c r="AA273" s="5"/>
       <c r="AB273" s="5"/>
@@ -10831,8 +11118,8 @@
       <c r="U274" s="5"/>
       <c r="V274" s="5"/>
       <c r="W274" s="5"/>
-      <c r="X274" s="5"/>
-      <c r="Y274" s="5"/>
+      <c r="X274" s="19"/>
+      <c r="Y274" s="38"/>
       <c r="Z274" s="5"/>
       <c r="AA274" s="5"/>
       <c r="AB274" s="5"/>
@@ -10865,8 +11152,8 @@
       <c r="U275" s="5"/>
       <c r="V275" s="5"/>
       <c r="W275" s="5"/>
-      <c r="X275" s="5"/>
-      <c r="Y275" s="5"/>
+      <c r="X275" s="19"/>
+      <c r="Y275" s="38"/>
       <c r="Z275" s="5"/>
       <c r="AA275" s="5"/>
       <c r="AB275" s="5"/>
@@ -10899,8 +11186,8 @@
       <c r="U276" s="5"/>
       <c r="V276" s="5"/>
       <c r="W276" s="5"/>
-      <c r="X276" s="5"/>
-      <c r="Y276" s="5"/>
+      <c r="X276" s="19"/>
+      <c r="Y276" s="38"/>
       <c r="Z276" s="5"/>
       <c r="AA276" s="5"/>
       <c r="AB276" s="5"/>
@@ -10933,8 +11220,8 @@
       <c r="U277" s="5"/>
       <c r="V277" s="5"/>
       <c r="W277" s="5"/>
-      <c r="X277" s="5"/>
-      <c r="Y277" s="5"/>
+      <c r="X277" s="19"/>
+      <c r="Y277" s="38"/>
       <c r="Z277" s="5"/>
       <c r="AA277" s="5"/>
       <c r="AB277" s="5"/>
@@ -10967,8 +11254,8 @@
       <c r="U278" s="5"/>
       <c r="V278" s="5"/>
       <c r="W278" s="5"/>
-      <c r="X278" s="5"/>
-      <c r="Y278" s="5"/>
+      <c r="X278" s="19"/>
+      <c r="Y278" s="38"/>
       <c r="Z278" s="5"/>
       <c r="AA278" s="5"/>
       <c r="AB278" s="5"/>
@@ -11001,8 +11288,8 @@
       <c r="U279" s="5"/>
       <c r="V279" s="5"/>
       <c r="W279" s="5"/>
-      <c r="X279" s="5"/>
-      <c r="Y279" s="5"/>
+      <c r="X279" s="19"/>
+      <c r="Y279" s="38"/>
       <c r="Z279" s="5"/>
       <c r="AA279" s="5"/>
       <c r="AB279" s="5"/>
@@ -11035,8 +11322,8 @@
       <c r="U280" s="5"/>
       <c r="V280" s="5"/>
       <c r="W280" s="5"/>
-      <c r="X280" s="5"/>
-      <c r="Y280" s="5"/>
+      <c r="X280" s="19"/>
+      <c r="Y280" s="38"/>
       <c r="Z280" s="5"/>
       <c r="AA280" s="5"/>
       <c r="AB280" s="5"/>
@@ -11069,8 +11356,8 @@
       <c r="U281" s="5"/>
       <c r="V281" s="5"/>
       <c r="W281" s="5"/>
-      <c r="X281" s="5"/>
-      <c r="Y281" s="5"/>
+      <c r="X281" s="19"/>
+      <c r="Y281" s="38"/>
       <c r="Z281" s="5"/>
       <c r="AA281" s="5"/>
       <c r="AB281" s="5"/>
@@ -11103,8 +11390,8 @@
       <c r="U282" s="5"/>
       <c r="V282" s="5"/>
       <c r="W282" s="5"/>
-      <c r="X282" s="5"/>
-      <c r="Y282" s="5"/>
+      <c r="X282" s="19"/>
+      <c r="Y282" s="38"/>
       <c r="Z282" s="5"/>
       <c r="AA282" s="5"/>
       <c r="AB282" s="5"/>
@@ -11137,8 +11424,8 @@
       <c r="U283" s="5"/>
       <c r="V283" s="5"/>
       <c r="W283" s="5"/>
-      <c r="X283" s="5"/>
-      <c r="Y283" s="5"/>
+      <c r="X283" s="19"/>
+      <c r="Y283" s="38"/>
       <c r="Z283" s="5"/>
       <c r="AA283" s="5"/>
       <c r="AB283" s="5"/>
@@ -11171,8 +11458,8 @@
       <c r="U284" s="5"/>
       <c r="V284" s="5"/>
       <c r="W284" s="5"/>
-      <c r="X284" s="5"/>
-      <c r="Y284" s="5"/>
+      <c r="X284" s="19"/>
+      <c r="Y284" s="38"/>
       <c r="Z284" s="5"/>
       <c r="AA284" s="5"/>
       <c r="AB284" s="5"/>
@@ -11205,8 +11492,8 @@
       <c r="U285" s="5"/>
       <c r="V285" s="5"/>
       <c r="W285" s="5"/>
-      <c r="X285" s="5"/>
-      <c r="Y285" s="5"/>
+      <c r="X285" s="19"/>
+      <c r="Y285" s="38"/>
       <c r="Z285" s="5"/>
       <c r="AA285" s="5"/>
       <c r="AB285" s="5"/>
@@ -11239,8 +11526,8 @@
       <c r="U286" s="5"/>
       <c r="V286" s="5"/>
       <c r="W286" s="5"/>
-      <c r="X286" s="5"/>
-      <c r="Y286" s="5"/>
+      <c r="X286" s="19"/>
+      <c r="Y286" s="38"/>
       <c r="Z286" s="5"/>
       <c r="AA286" s="5"/>
       <c r="AB286" s="5"/>
@@ -11273,8 +11560,8 @@
       <c r="U287" s="5"/>
       <c r="V287" s="5"/>
       <c r="W287" s="5"/>
-      <c r="X287" s="5"/>
-      <c r="Y287" s="5"/>
+      <c r="X287" s="19"/>
+      <c r="Y287" s="38"/>
       <c r="Z287" s="5"/>
       <c r="AA287" s="5"/>
       <c r="AB287" s="5"/>
@@ -11307,8 +11594,8 @@
       <c r="U288" s="5"/>
       <c r="V288" s="5"/>
       <c r="W288" s="5"/>
-      <c r="X288" s="5"/>
-      <c r="Y288" s="5"/>
+      <c r="X288" s="19"/>
+      <c r="Y288" s="38"/>
       <c r="Z288" s="5"/>
       <c r="AA288" s="5"/>
       <c r="AB288" s="5"/>
@@ -11341,8 +11628,8 @@
       <c r="U289" s="5"/>
       <c r="V289" s="5"/>
       <c r="W289" s="5"/>
-      <c r="X289" s="5"/>
-      <c r="Y289" s="5"/>
+      <c r="X289" s="19"/>
+      <c r="Y289" s="38"/>
       <c r="Z289" s="5"/>
       <c r="AA289" s="5"/>
       <c r="AB289" s="5"/>
@@ -11375,8 +11662,8 @@
       <c r="U290" s="5"/>
       <c r="V290" s="5"/>
       <c r="W290" s="5"/>
-      <c r="X290" s="5"/>
-      <c r="Y290" s="5"/>
+      <c r="X290" s="19"/>
+      <c r="Y290" s="38"/>
       <c r="Z290" s="5"/>
       <c r="AA290" s="5"/>
       <c r="AB290" s="5"/>
@@ -11409,8 +11696,8 @@
       <c r="U291" s="5"/>
       <c r="V291" s="5"/>
       <c r="W291" s="5"/>
-      <c r="X291" s="5"/>
-      <c r="Y291" s="5"/>
+      <c r="X291" s="19"/>
+      <c r="Y291" s="38"/>
       <c r="Z291" s="5"/>
       <c r="AA291" s="5"/>
       <c r="AB291" s="5"/>
@@ -11443,8 +11730,8 @@
       <c r="U292" s="5"/>
       <c r="V292" s="5"/>
       <c r="W292" s="5"/>
-      <c r="X292" s="5"/>
-      <c r="Y292" s="5"/>
+      <c r="X292" s="19"/>
+      <c r="Y292" s="38"/>
       <c r="Z292" s="5"/>
       <c r="AA292" s="5"/>
       <c r="AB292" s="5"/>
@@ -11477,8 +11764,8 @@
       <c r="U293" s="5"/>
       <c r="V293" s="5"/>
       <c r="W293" s="5"/>
-      <c r="X293" s="5"/>
-      <c r="Y293" s="5"/>
+      <c r="X293" s="19"/>
+      <c r="Y293" s="38"/>
       <c r="Z293" s="5"/>
       <c r="AA293" s="5"/>
       <c r="AB293" s="5"/>
@@ -11511,8 +11798,8 @@
       <c r="U294" s="5"/>
       <c r="V294" s="5"/>
       <c r="W294" s="5"/>
-      <c r="X294" s="5"/>
-      <c r="Y294" s="5"/>
+      <c r="X294" s="19"/>
+      <c r="Y294" s="38"/>
       <c r="Z294" s="5"/>
       <c r="AA294" s="5"/>
       <c r="AB294" s="5"/>
@@ -11545,8 +11832,8 @@
       <c r="U295" s="5"/>
       <c r="V295" s="5"/>
       <c r="W295" s="5"/>
-      <c r="X295" s="5"/>
-      <c r="Y295" s="5"/>
+      <c r="X295" s="19"/>
+      <c r="Y295" s="38"/>
       <c r="Z295" s="5"/>
       <c r="AA295" s="5"/>
       <c r="AB295" s="5"/>
@@ -11579,8 +11866,8 @@
       <c r="U296" s="5"/>
       <c r="V296" s="5"/>
       <c r="W296" s="5"/>
-      <c r="X296" s="5"/>
-      <c r="Y296" s="5"/>
+      <c r="X296" s="19"/>
+      <c r="Y296" s="38"/>
       <c r="Z296" s="5"/>
       <c r="AA296" s="5"/>
       <c r="AB296" s="5"/>
@@ -11613,8 +11900,8 @@
       <c r="U297" s="5"/>
       <c r="V297" s="5"/>
       <c r="W297" s="5"/>
-      <c r="X297" s="5"/>
-      <c r="Y297" s="5"/>
+      <c r="X297" s="19"/>
+      <c r="Y297" s="38"/>
       <c r="Z297" s="5"/>
       <c r="AA297" s="5"/>
       <c r="AB297" s="5"/>
@@ -11647,8 +11934,8 @@
       <c r="U298" s="5"/>
       <c r="V298" s="5"/>
       <c r="W298" s="5"/>
-      <c r="X298" s="5"/>
-      <c r="Y298" s="5"/>
+      <c r="X298" s="19"/>
+      <c r="Y298" s="38"/>
       <c r="Z298" s="5"/>
       <c r="AA298" s="5"/>
       <c r="AB298" s="5"/>
@@ -11681,8 +11968,8 @@
       <c r="U299" s="5"/>
       <c r="V299" s="5"/>
       <c r="W299" s="5"/>
-      <c r="X299" s="5"/>
-      <c r="Y299" s="5"/>
+      <c r="X299" s="19"/>
+      <c r="Y299" s="38"/>
       <c r="Z299" s="5"/>
       <c r="AA299" s="5"/>
       <c r="AB299" s="5"/>
@@ -11715,8 +12002,8 @@
       <c r="U300" s="5"/>
       <c r="V300" s="5"/>
       <c r="W300" s="5"/>
-      <c r="X300" s="5"/>
-      <c r="Y300" s="5"/>
+      <c r="X300" s="19"/>
+      <c r="Y300" s="38"/>
       <c r="Z300" s="5"/>
       <c r="AA300" s="5"/>
       <c r="AB300" s="5"/>
@@ -11749,8 +12036,8 @@
       <c r="U301" s="5"/>
       <c r="V301" s="5"/>
       <c r="W301" s="5"/>
-      <c r="X301" s="5"/>
-      <c r="Y301" s="5"/>
+      <c r="X301" s="19"/>
+      <c r="Y301" s="38"/>
       <c r="Z301" s="5"/>
       <c r="AA301" s="5"/>
       <c r="AB301" s="5"/>
@@ -11783,8 +12070,8 @@
       <c r="U302" s="5"/>
       <c r="V302" s="5"/>
       <c r="W302" s="5"/>
-      <c r="X302" s="5"/>
-      <c r="Y302" s="5"/>
+      <c r="X302" s="19"/>
+      <c r="Y302" s="38"/>
       <c r="Z302" s="5"/>
       <c r="AA302" s="5"/>
       <c r="AB302" s="5"/>
@@ -11817,8 +12104,8 @@
       <c r="U303" s="5"/>
       <c r="V303" s="5"/>
       <c r="W303" s="5"/>
-      <c r="X303" s="5"/>
-      <c r="Y303" s="5"/>
+      <c r="X303" s="19"/>
+      <c r="Y303" s="38"/>
       <c r="Z303" s="5"/>
       <c r="AA303" s="5"/>
       <c r="AB303" s="5"/>
@@ -11851,8 +12138,8 @@
       <c r="U304" s="5"/>
       <c r="V304" s="5"/>
       <c r="W304" s="5"/>
-      <c r="X304" s="5"/>
-      <c r="Y304" s="5"/>
+      <c r="X304" s="19"/>
+      <c r="Y304" s="38"/>
       <c r="Z304" s="5"/>
       <c r="AA304" s="5"/>
       <c r="AB304" s="5"/>
@@ -11885,8 +12172,8 @@
       <c r="U305" s="5"/>
       <c r="V305" s="5"/>
       <c r="W305" s="5"/>
-      <c r="X305" s="5"/>
-      <c r="Y305" s="5"/>
+      <c r="X305" s="19"/>
+      <c r="Y305" s="38"/>
       <c r="Z305" s="5"/>
       <c r="AA305" s="5"/>
       <c r="AB305" s="5"/>
@@ -11919,8 +12206,8 @@
       <c r="U306" s="5"/>
       <c r="V306" s="5"/>
       <c r="W306" s="5"/>
-      <c r="X306" s="5"/>
-      <c r="Y306" s="5"/>
+      <c r="X306" s="19"/>
+      <c r="Y306" s="38"/>
       <c r="Z306" s="5"/>
       <c r="AA306" s="5"/>
       <c r="AB306" s="5"/>
@@ -11953,8 +12240,8 @@
       <c r="U307" s="5"/>
       <c r="V307" s="5"/>
       <c r="W307" s="5"/>
-      <c r="X307" s="5"/>
-      <c r="Y307" s="5"/>
+      <c r="X307" s="19"/>
+      <c r="Y307" s="38"/>
       <c r="Z307" s="5"/>
       <c r="AA307" s="5"/>
       <c r="AB307" s="5"/>
@@ -11987,8 +12274,8 @@
       <c r="U308" s="5"/>
       <c r="V308" s="5"/>
       <c r="W308" s="5"/>
-      <c r="X308" s="5"/>
-      <c r="Y308" s="5"/>
+      <c r="X308" s="19"/>
+      <c r="Y308" s="38"/>
       <c r="Z308" s="5"/>
       <c r="AA308" s="5"/>
       <c r="AB308" s="5"/>
@@ -12021,8 +12308,8 @@
       <c r="U309" s="5"/>
       <c r="V309" s="5"/>
       <c r="W309" s="5"/>
-      <c r="X309" s="5"/>
-      <c r="Y309" s="5"/>
+      <c r="X309" s="19"/>
+      <c r="Y309" s="38"/>
       <c r="Z309" s="5"/>
       <c r="AA309" s="5"/>
       <c r="AB309" s="5"/>
@@ -12055,8 +12342,8 @@
       <c r="U310" s="5"/>
       <c r="V310" s="5"/>
       <c r="W310" s="5"/>
-      <c r="X310" s="5"/>
-      <c r="Y310" s="5"/>
+      <c r="X310" s="19"/>
+      <c r="Y310" s="38"/>
       <c r="Z310" s="5"/>
       <c r="AA310" s="5"/>
       <c r="AB310" s="5"/>
@@ -12089,8 +12376,8 @@
       <c r="U311" s="5"/>
       <c r="V311" s="5"/>
       <c r="W311" s="5"/>
-      <c r="X311" s="5"/>
-      <c r="Y311" s="5"/>
+      <c r="X311" s="19"/>
+      <c r="Y311" s="38"/>
       <c r="Z311" s="5"/>
       <c r="AA311" s="5"/>
       <c r="AB311" s="5"/>
@@ -12123,8 +12410,8 @@
       <c r="U312" s="5"/>
       <c r="V312" s="5"/>
       <c r="W312" s="5"/>
-      <c r="X312" s="5"/>
-      <c r="Y312" s="5"/>
+      <c r="X312" s="19"/>
+      <c r="Y312" s="38"/>
       <c r="Z312" s="5"/>
       <c r="AA312" s="5"/>
       <c r="AB312" s="5"/>
@@ -12157,8 +12444,8 @@
       <c r="U313" s="5"/>
       <c r="V313" s="5"/>
       <c r="W313" s="5"/>
-      <c r="X313" s="5"/>
-      <c r="Y313" s="5"/>
+      <c r="X313" s="19"/>
+      <c r="Y313" s="38"/>
       <c r="Z313" s="5"/>
       <c r="AA313" s="5"/>
       <c r="AB313" s="5"/>
@@ -12191,8 +12478,8 @@
       <c r="U314" s="5"/>
       <c r="V314" s="5"/>
       <c r="W314" s="5"/>
-      <c r="X314" s="5"/>
-      <c r="Y314" s="5"/>
+      <c r="X314" s="19"/>
+      <c r="Y314" s="38"/>
       <c r="Z314" s="5"/>
       <c r="AA314" s="5"/>
       <c r="AB314" s="5"/>
@@ -12225,8 +12512,8 @@
       <c r="U315" s="5"/>
       <c r="V315" s="5"/>
       <c r="W315" s="5"/>
-      <c r="X315" s="5"/>
-      <c r="Y315" s="5"/>
+      <c r="X315" s="19"/>
+      <c r="Y315" s="38"/>
       <c r="Z315" s="5"/>
       <c r="AA315" s="5"/>
       <c r="AB315" s="5"/>
@@ -12259,8 +12546,8 @@
       <c r="U316" s="5"/>
       <c r="V316" s="5"/>
       <c r="W316" s="5"/>
-      <c r="X316" s="5"/>
-      <c r="Y316" s="5"/>
+      <c r="X316" s="19"/>
+      <c r="Y316" s="38"/>
       <c r="Z316" s="5"/>
       <c r="AA316" s="5"/>
       <c r="AB316" s="5"/>
@@ -12293,8 +12580,8 @@
       <c r="U317" s="5"/>
       <c r="V317" s="5"/>
       <c r="W317" s="5"/>
-      <c r="X317" s="5"/>
-      <c r="Y317" s="5"/>
+      <c r="X317" s="19"/>
+      <c r="Y317" s="38"/>
       <c r="Z317" s="5"/>
       <c r="AA317" s="5"/>
       <c r="AB317" s="5"/>
@@ -12327,8 +12614,8 @@
       <c r="U318" s="5"/>
       <c r="V318" s="5"/>
       <c r="W318" s="5"/>
-      <c r="X318" s="5"/>
-      <c r="Y318" s="5"/>
+      <c r="X318" s="19"/>
+      <c r="Y318" s="38"/>
       <c r="Z318" s="5"/>
       <c r="AA318" s="5"/>
       <c r="AB318" s="5"/>
@@ -12361,8 +12648,8 @@
       <c r="U319" s="5"/>
       <c r="V319" s="5"/>
       <c r="W319" s="5"/>
-      <c r="X319" s="5"/>
-      <c r="Y319" s="5"/>
+      <c r="X319" s="19"/>
+      <c r="Y319" s="38"/>
       <c r="Z319" s="5"/>
       <c r="AA319" s="5"/>
       <c r="AB319" s="5"/>
@@ -12395,8 +12682,8 @@
       <c r="U320" s="5"/>
       <c r="V320" s="5"/>
       <c r="W320" s="5"/>
-      <c r="X320" s="5"/>
-      <c r="Y320" s="5"/>
+      <c r="X320" s="19"/>
+      <c r="Y320" s="38"/>
       <c r="Z320" s="5"/>
       <c r="AA320" s="5"/>
       <c r="AB320" s="5"/>
@@ -12429,8 +12716,8 @@
       <c r="U321" s="5"/>
       <c r="V321" s="5"/>
       <c r="W321" s="5"/>
-      <c r="X321" s="5"/>
-      <c r="Y321" s="5"/>
+      <c r="X321" s="19"/>
+      <c r="Y321" s="38"/>
       <c r="Z321" s="5"/>
       <c r="AA321" s="5"/>
       <c r="AB321" s="5"/>
@@ -12463,8 +12750,8 @@
       <c r="U322" s="5"/>
       <c r="V322" s="5"/>
       <c r="W322" s="5"/>
-      <c r="X322" s="5"/>
-      <c r="Y322" s="5"/>
+      <c r="X322" s="19"/>
+      <c r="Y322" s="38"/>
       <c r="Z322" s="5"/>
       <c r="AA322" s="5"/>
       <c r="AB322" s="5"/>
@@ -12497,8 +12784,8 @@
       <c r="U323" s="5"/>
       <c r="V323" s="5"/>
       <c r="W323" s="5"/>
-      <c r="X323" s="5"/>
-      <c r="Y323" s="5"/>
+      <c r="X323" s="19"/>
+      <c r="Y323" s="38"/>
       <c r="Z323" s="5"/>
       <c r="AA323" s="5"/>
       <c r="AB323" s="5"/>
@@ -12531,8 +12818,8 @@
       <c r="U324" s="5"/>
       <c r="V324" s="5"/>
       <c r="W324" s="5"/>
-      <c r="X324" s="5"/>
-      <c r="Y324" s="5"/>
+      <c r="X324" s="19"/>
+      <c r="Y324" s="38"/>
       <c r="Z324" s="5"/>
       <c r="AA324" s="5"/>
       <c r="AB324" s="5"/>
@@ -12565,8 +12852,8 @@
       <c r="U325" s="5"/>
       <c r="V325" s="5"/>
       <c r="W325" s="5"/>
-      <c r="X325" s="5"/>
-      <c r="Y325" s="5"/>
+      <c r="X325" s="19"/>
+      <c r="Y325" s="38"/>
       <c r="Z325" s="5"/>
       <c r="AA325" s="5"/>
       <c r="AB325" s="5"/>
@@ -12599,8 +12886,8 @@
       <c r="U326" s="5"/>
       <c r="V326" s="5"/>
       <c r="W326" s="5"/>
-      <c r="X326" s="5"/>
-      <c r="Y326" s="5"/>
+      <c r="X326" s="19"/>
+      <c r="Y326" s="38"/>
       <c r="Z326" s="5"/>
       <c r="AA326" s="5"/>
       <c r="AB326" s="5"/>
@@ -12633,8 +12920,8 @@
       <c r="U327" s="5"/>
       <c r="V327" s="5"/>
       <c r="W327" s="5"/>
-      <c r="X327" s="5"/>
-      <c r="Y327" s="5"/>
+      <c r="X327" s="19"/>
+      <c r="Y327" s="38"/>
       <c r="Z327" s="5"/>
       <c r="AA327" s="5"/>
       <c r="AB327" s="5"/>
@@ -12667,8 +12954,8 @@
       <c r="U328" s="5"/>
       <c r="V328" s="5"/>
       <c r="W328" s="5"/>
-      <c r="X328" s="5"/>
-      <c r="Y328" s="5"/>
+      <c r="X328" s="19"/>
+      <c r="Y328" s="38"/>
       <c r="Z328" s="5"/>
       <c r="AA328" s="5"/>
       <c r="AB328" s="5"/>
@@ -12701,8 +12988,8 @@
       <c r="U329" s="5"/>
       <c r="V329" s="5"/>
       <c r="W329" s="5"/>
-      <c r="X329" s="5"/>
-      <c r="Y329" s="5"/>
+      <c r="X329" s="19"/>
+      <c r="Y329" s="38"/>
       <c r="Z329" s="5"/>
       <c r="AA329" s="5"/>
       <c r="AB329" s="5"/>
@@ -12735,8 +13022,8 @@
       <c r="U330" s="5"/>
       <c r="V330" s="5"/>
       <c r="W330" s="5"/>
-      <c r="X330" s="5"/>
-      <c r="Y330" s="5"/>
+      <c r="X330" s="19"/>
+      <c r="Y330" s="38"/>
       <c r="Z330" s="5"/>
       <c r="AA330" s="5"/>
       <c r="AB330" s="5"/>
@@ -12769,8 +13056,8 @@
       <c r="U331" s="5"/>
       <c r="V331" s="5"/>
       <c r="W331" s="5"/>
-      <c r="X331" s="5"/>
-      <c r="Y331" s="5"/>
+      <c r="X331" s="19"/>
+      <c r="Y331" s="38"/>
       <c r="Z331" s="5"/>
       <c r="AA331" s="5"/>
       <c r="AB331" s="5"/>
@@ -12803,8 +13090,8 @@
       <c r="U332" s="5"/>
       <c r="V332" s="5"/>
       <c r="W332" s="5"/>
-      <c r="X332" s="5"/>
-      <c r="Y332" s="5"/>
+      <c r="X332" s="19"/>
+      <c r="Y332" s="38"/>
       <c r="Z332" s="5"/>
       <c r="AA332" s="5"/>
       <c r="AB332" s="5"/>
@@ -12837,8 +13124,8 @@
       <c r="U333" s="5"/>
       <c r="V333" s="5"/>
       <c r="W333" s="5"/>
-      <c r="X333" s="5"/>
-      <c r="Y333" s="5"/>
+      <c r="X333" s="19"/>
+      <c r="Y333" s="38"/>
       <c r="Z333" s="5"/>
       <c r="AA333" s="5"/>
       <c r="AB333" s="5"/>
@@ -12871,8 +13158,8 @@
       <c r="U334" s="5"/>
       <c r="V334" s="5"/>
       <c r="W334" s="5"/>
-      <c r="X334" s="5"/>
-      <c r="Y334" s="5"/>
+      <c r="X334" s="19"/>
+      <c r="Y334" s="38"/>
       <c r="Z334" s="5"/>
       <c r="AA334" s="5"/>
       <c r="AB334" s="5"/>
@@ -12884,6 +13171,19 @@
     <row r="335" spans="1:32" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A67:W67"/>
+    <mergeCell ref="A30:W30"/>
+    <mergeCell ref="O2:R2"/>
+    <mergeCell ref="A59:W59"/>
+    <mergeCell ref="A73:W73"/>
+    <mergeCell ref="A24:W24"/>
+    <mergeCell ref="A11:W11"/>
+    <mergeCell ref="A36:W36"/>
+    <mergeCell ref="A17:W17"/>
+    <mergeCell ref="A53:W53"/>
+    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="A20:W20"/>
+    <mergeCell ref="K2:N2"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A45:W45"/>
     <mergeCell ref="A103:W103"/>
@@ -12900,22 +13200,236 @@
     <mergeCell ref="A95:W95"/>
     <mergeCell ref="A85:W85"/>
     <mergeCell ref="A5:W5"/>
-    <mergeCell ref="A67:W67"/>
-    <mergeCell ref="A30:W30"/>
-    <mergeCell ref="O2:R2"/>
-    <mergeCell ref="A59:W59"/>
-    <mergeCell ref="A73:W73"/>
-    <mergeCell ref="A24:W24"/>
-    <mergeCell ref="A11:W11"/>
-    <mergeCell ref="A36:W36"/>
-    <mergeCell ref="A17:W17"/>
-    <mergeCell ref="A53:W53"/>
-    <mergeCell ref="A4:W4"/>
-    <mergeCell ref="A20:W20"/>
-    <mergeCell ref="K2:N2"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="4a37abda-15dd-4e37-8275-3b7fb2897b65" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="74a0992f-8328-4daf-870b-3d2b13d3e940">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AB003DB5A4D644C9FB3BD19B5C7E000" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2c3211479268aeb6d058ac20e4430716">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="74a0992f-8328-4daf-870b-3d2b13d3e940" xmlns:ns3="4a37abda-15dd-4e37-8275-3b7fb2897b65" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d78d1d4c9cad7b16b9dee64e4ff3a833" ns2:_="" ns3:_="">
+    <xsd:import namespace="74a0992f-8328-4daf-870b-3d2b13d3e940"/>
+    <xsd:import namespace="4a37abda-15dd-4e37-8275-3b7fb2897b65"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="74a0992f-8328-4daf-870b-3d2b13d3e940" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="e6619b5c-6674-40b7-9c01-33e12ba1bd7c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4a37abda-15dd-4e37-8275-3b7fb2897b65" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="17" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f2a2e70a-4904-448e-b588-7989bbdb9dd5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="4a37abda-15dd-4e37-8275-3b7fb2897b65">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60E533D7-F71C-48F2-9934-5B1CF7429AB2}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{501917D9-78A0-4206-A139-93ECC85721A9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0286D6A2-D9BB-4F04-8D55-9EA841E8D484}"/>
 </file>